--- a/VerveStacks_MEX_grids_kan/vt_vervestacks_MEX_v1.xlsx
+++ b/VerveStacks_MEX_grids_kan/vt_vervestacks_MEX_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EC9F9B3-030F-4025-8846-234ED3245116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91E28A88-61C1-47BC-8480-19A3A645B0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9FD84AB6-1FDB-4912-AE69-E6D6B3597D52}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1A5B4945-F7C3-4342-BF4F-7187E21BB802}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3898,7 +3898,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BD547D-B913-4E76-A636-847CE0537866}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C46F0B0-3FA7-4F00-A21F-77C3BEBA6DE1}">
   <dimension ref="B9:V177"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3986,7 +3986,7 @@
         <v>38</v>
       </c>
       <c r="F11">
-        <v>7.350656160000002E-2</v>
+        <v>6.1423291200000014E-2</v>
       </c>
       <c r="G11">
         <v>3583</v>
@@ -4048,7 +4048,7 @@
         <v>40</v>
       </c>
       <c r="F12">
-        <v>7.323360000000001E-2</v>
+        <v>6.1195200000000012E-2</v>
       </c>
       <c r="G12">
         <v>3583</v>
@@ -4110,7 +4110,7 @@
         <v>40</v>
       </c>
       <c r="F13">
-        <v>7.323360000000001E-2</v>
+        <v>6.1195200000000012E-2</v>
       </c>
       <c r="G13">
         <v>3583</v>
@@ -4172,7 +4172,7 @@
         <v>40</v>
       </c>
       <c r="F14">
-        <v>7.323360000000001E-2</v>
+        <v>6.1195200000000012E-2</v>
       </c>
       <c r="G14">
         <v>3583</v>
@@ -4234,7 +4234,7 @@
         <v>40</v>
       </c>
       <c r="F15">
-        <v>7.323360000000001E-2</v>
+        <v>6.1195200000000012E-2</v>
       </c>
       <c r="G15">
         <v>3583</v>
@@ -4296,7 +4296,7 @@
         <v>40</v>
       </c>
       <c r="F16">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G16">
         <v>3583</v>
@@ -4358,7 +4358,7 @@
         <v>40</v>
       </c>
       <c r="F17">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G17">
         <v>3583</v>
@@ -4420,7 +4420,7 @@
         <v>40</v>
       </c>
       <c r="F18">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G18">
         <v>3583</v>
@@ -4482,7 +4482,7 @@
         <v>40</v>
       </c>
       <c r="F19">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G19">
         <v>3583</v>
@@ -4544,7 +4544,7 @@
         <v>49</v>
       </c>
       <c r="F20">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G20">
         <v>3583</v>
@@ -4606,7 +4606,7 @@
         <v>49</v>
       </c>
       <c r="F21">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G21">
         <v>3583</v>
@@ -4668,7 +4668,7 @@
         <v>49</v>
       </c>
       <c r="F22">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G22">
         <v>3583</v>
@@ -4730,7 +4730,7 @@
         <v>49</v>
       </c>
       <c r="F23">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G23">
         <v>3583</v>
@@ -4792,7 +4792,7 @@
         <v>49</v>
       </c>
       <c r="F24">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G24">
         <v>3583</v>
@@ -4854,7 +4854,7 @@
         <v>49</v>
       </c>
       <c r="F25">
-        <v>7.9891200000000009E-2</v>
+        <v>6.6758400000000009E-2</v>
       </c>
       <c r="G25">
         <v>3583</v>
@@ -4916,7 +4916,7 @@
         <v>49</v>
       </c>
       <c r="F26">
-        <v>0.20011490000000001</v>
+        <v>0.16721930000000002</v>
       </c>
       <c r="G26">
         <v>2445</v>
@@ -4978,7 +4978,7 @@
         <v>58</v>
       </c>
       <c r="F27">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G27">
         <v>1365</v>
@@ -5040,7 +5040,7 @@
         <v>60</v>
       </c>
       <c r="F28">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G28">
         <v>1365</v>
@@ -5102,7 +5102,7 @@
         <v>60</v>
       </c>
       <c r="F29">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G29">
         <v>1365</v>
@@ -5164,7 +5164,7 @@
         <v>63</v>
       </c>
       <c r="F30">
-        <v>0.370475</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G30">
         <v>1365</v>
@@ -5226,7 +5226,7 @@
         <v>65</v>
       </c>
       <c r="F31">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G31">
         <v>1365</v>
@@ -5288,7 +5288,7 @@
         <v>67</v>
       </c>
       <c r="F32">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G32">
         <v>1365</v>
@@ -5350,7 +5350,7 @@
         <v>67</v>
       </c>
       <c r="F33">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999999</v>
       </c>
       <c r="G33">
         <v>1365</v>
@@ -5412,7 +5412,7 @@
         <v>70</v>
       </c>
       <c r="F34">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999992</v>
       </c>
       <c r="G34">
         <v>1365</v>
@@ -5474,7 +5474,7 @@
         <v>63</v>
       </c>
       <c r="F35">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G35">
         <v>1365</v>
@@ -5536,7 +5536,7 @@
         <v>73</v>
       </c>
       <c r="F36">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999999</v>
       </c>
       <c r="G36">
         <v>1365</v>
@@ -5598,7 +5598,7 @@
         <v>75</v>
       </c>
       <c r="F37">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G37">
         <v>1365</v>
@@ -5660,7 +5660,7 @@
         <v>77</v>
       </c>
       <c r="F38">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G38">
         <v>1365</v>
@@ -5722,7 +5722,7 @@
         <v>79</v>
       </c>
       <c r="F39">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G39">
         <v>1365</v>
@@ -5784,7 +5784,7 @@
         <v>81</v>
       </c>
       <c r="F40">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G40">
         <v>1365</v>
@@ -5846,7 +5846,7 @@
         <v>81</v>
       </c>
       <c r="F41">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G41">
         <v>1365</v>
@@ -5908,7 +5908,7 @@
         <v>81</v>
       </c>
       <c r="F42">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G42">
         <v>1365</v>
@@ -5970,7 +5970,7 @@
         <v>85</v>
       </c>
       <c r="F43">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G43">
         <v>1365</v>
@@ -6032,7 +6032,7 @@
         <v>85</v>
       </c>
       <c r="F44">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G44">
         <v>1365</v>
@@ -6094,7 +6094,7 @@
         <v>88</v>
       </c>
       <c r="F45">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G45">
         <v>1365</v>
@@ -6156,7 +6156,7 @@
         <v>88</v>
       </c>
       <c r="F46">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G46">
         <v>1365</v>
@@ -6218,7 +6218,7 @@
         <v>91</v>
       </c>
       <c r="F47">
-        <v>0.33534375</v>
+        <v>0.28021874999999996</v>
       </c>
       <c r="G47">
         <v>1365</v>
@@ -6280,7 +6280,7 @@
         <v>91</v>
       </c>
       <c r="F48">
-        <v>0.28743750000000001</v>
+        <v>0.2401875</v>
       </c>
       <c r="G48">
         <v>1365</v>
@@ -6342,7 +6342,7 @@
         <v>88</v>
       </c>
       <c r="F49">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G49">
         <v>1365</v>
@@ -6404,7 +6404,7 @@
         <v>81</v>
       </c>
       <c r="F50">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G50">
         <v>1365</v>
@@ -6466,7 +6466,7 @@
         <v>96</v>
       </c>
       <c r="F51">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999988</v>
       </c>
       <c r="G51">
         <v>1365</v>
@@ -6528,7 +6528,7 @@
         <v>96</v>
       </c>
       <c r="F52">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999999</v>
       </c>
       <c r="G52">
         <v>1365</v>
@@ -6590,7 +6590,7 @@
         <v>99</v>
       </c>
       <c r="F53">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G53">
         <v>1365</v>
@@ -6652,7 +6652,7 @@
         <v>77</v>
       </c>
       <c r="F54">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G54">
         <v>1365</v>
@@ -6714,7 +6714,7 @@
         <v>60</v>
       </c>
       <c r="F55">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G55">
         <v>1365</v>
@@ -6776,7 +6776,7 @@
         <v>103</v>
       </c>
       <c r="F56">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G56">
         <v>1365</v>
@@ -6838,7 +6838,7 @@
         <v>88</v>
       </c>
       <c r="F57">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999992</v>
       </c>
       <c r="G57">
         <v>1365</v>
@@ -6900,7 +6900,7 @@
         <v>106</v>
       </c>
       <c r="F58">
-        <v>0.38325000000000004</v>
+        <v>0.32025000000000003</v>
       </c>
       <c r="G58">
         <v>1365</v>
@@ -6962,7 +6962,7 @@
         <v>103</v>
       </c>
       <c r="F59">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G59">
         <v>1365</v>
@@ -7024,7 +7024,7 @@
         <v>109</v>
       </c>
       <c r="F60">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G60">
         <v>1365</v>
@@ -7086,7 +7086,7 @@
         <v>111</v>
       </c>
       <c r="F61">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G61">
         <v>1365</v>
@@ -7148,7 +7148,7 @@
         <v>113</v>
       </c>
       <c r="F62">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G62">
         <v>1365</v>
@@ -7210,7 +7210,7 @@
         <v>115</v>
       </c>
       <c r="F63">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G63">
         <v>1365</v>
@@ -7272,7 +7272,7 @@
         <v>115</v>
       </c>
       <c r="F64">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G64">
         <v>1365</v>
@@ -7334,7 +7334,7 @@
         <v>118</v>
       </c>
       <c r="F65">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G65">
         <v>1365</v>
@@ -7396,7 +7396,7 @@
         <v>118</v>
       </c>
       <c r="F66">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G66">
         <v>1365</v>
@@ -7458,7 +7458,7 @@
         <v>118</v>
       </c>
       <c r="F67">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G67">
         <v>1365</v>
@@ -7520,7 +7520,7 @@
         <v>118</v>
       </c>
       <c r="F68">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G68">
         <v>1365</v>
@@ -7582,7 +7582,7 @@
         <v>123</v>
       </c>
       <c r="F69">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G69">
         <v>1365</v>
@@ -7644,7 +7644,7 @@
         <v>125</v>
       </c>
       <c r="F70">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G70">
         <v>1365</v>
@@ -7706,7 +7706,7 @@
         <v>127</v>
       </c>
       <c r="F71">
-        <v>0.33534375</v>
+        <v>0.28021874999999996</v>
       </c>
       <c r="G71">
         <v>1365</v>
@@ -7768,7 +7768,7 @@
         <v>129</v>
       </c>
       <c r="F72">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G72">
         <v>1365</v>
@@ -7830,7 +7830,7 @@
         <v>127</v>
       </c>
       <c r="F73">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G73">
         <v>1365</v>
@@ -7892,7 +7892,7 @@
         <v>132</v>
       </c>
       <c r="F74">
-        <v>0.33534375</v>
+        <v>0.28021874999999996</v>
       </c>
       <c r="G74">
         <v>1365</v>
@@ -7954,7 +7954,7 @@
         <v>134</v>
       </c>
       <c r="F75">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G75">
         <v>1365</v>
@@ -8016,7 +8016,7 @@
         <v>134</v>
       </c>
       <c r="F76">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G76">
         <v>1365</v>
@@ -8078,7 +8078,7 @@
         <v>134</v>
       </c>
       <c r="F77">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G77">
         <v>1365</v>
@@ -8140,7 +8140,7 @@
         <v>138</v>
       </c>
       <c r="F78">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G78">
         <v>1365</v>
@@ -8202,7 +8202,7 @@
         <v>138</v>
       </c>
       <c r="F79">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G79">
         <v>1365</v>
@@ -8264,7 +8264,7 @@
         <v>132</v>
       </c>
       <c r="F80">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G80">
         <v>1365</v>
@@ -8326,7 +8326,7 @@
         <v>91</v>
       </c>
       <c r="F81">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G81">
         <v>1365</v>
@@ -8388,7 +8388,7 @@
         <v>91</v>
       </c>
       <c r="F82">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G82">
         <v>1365</v>
@@ -8450,7 +8450,7 @@
         <v>144</v>
       </c>
       <c r="F83">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G83">
         <v>1365</v>
@@ -8512,7 +8512,7 @@
         <v>88</v>
       </c>
       <c r="F84">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G84">
         <v>1365</v>
@@ -8574,7 +8574,7 @@
         <v>75</v>
       </c>
       <c r="F85">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G85">
         <v>1365</v>
@@ -8636,7 +8636,7 @@
         <v>75</v>
       </c>
       <c r="F86">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G86">
         <v>1365</v>
@@ -8698,7 +8698,7 @@
         <v>75</v>
       </c>
       <c r="F87">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G87">
         <v>1365</v>
@@ -8760,7 +8760,7 @@
         <v>75</v>
       </c>
       <c r="F88">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G88">
         <v>1365</v>
@@ -8822,7 +8822,7 @@
         <v>81</v>
       </c>
       <c r="F89">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G89">
         <v>1365</v>
@@ -8884,7 +8884,7 @@
         <v>91</v>
       </c>
       <c r="F90">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G90">
         <v>1365</v>
@@ -8946,7 +8946,7 @@
         <v>91</v>
       </c>
       <c r="F91">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G91">
         <v>1365</v>
@@ -9008,7 +9008,7 @@
         <v>91</v>
       </c>
       <c r="F92">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G92">
         <v>1365</v>
@@ -9070,7 +9070,7 @@
         <v>58</v>
       </c>
       <c r="F93">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G93">
         <v>1365</v>
@@ -9132,7 +9132,7 @@
         <v>58</v>
       </c>
       <c r="F94">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G94">
         <v>1365</v>
@@ -9194,7 +9194,7 @@
         <v>157</v>
       </c>
       <c r="F95">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G95">
         <v>1365</v>
@@ -9256,7 +9256,7 @@
         <v>88</v>
       </c>
       <c r="F96">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G96">
         <v>1365</v>
@@ -9318,7 +9318,7 @@
         <v>75</v>
       </c>
       <c r="F97">
-        <v>0.34811875000000003</v>
+        <v>0.29089375000000001</v>
       </c>
       <c r="G97">
         <v>1365</v>
@@ -9380,7 +9380,7 @@
         <v>99</v>
       </c>
       <c r="F98">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G98">
         <v>1365</v>
@@ -9442,7 +9442,7 @@
         <v>28</v>
       </c>
       <c r="F99">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G99">
         <v>1365</v>
@@ -9504,7 +9504,7 @@
         <v>28</v>
       </c>
       <c r="F100">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G100">
         <v>1365</v>
@@ -9566,7 +9566,7 @@
         <v>88</v>
       </c>
       <c r="F101">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G101">
         <v>1365</v>
@@ -9628,7 +9628,7 @@
         <v>88</v>
       </c>
       <c r="F102">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G102">
         <v>1365</v>
@@ -9690,7 +9690,7 @@
         <v>88</v>
       </c>
       <c r="F103">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G103">
         <v>1365</v>
@@ -9752,7 +9752,7 @@
         <v>85</v>
       </c>
       <c r="F104">
-        <v>0.38325000000000004</v>
+        <v>0.32025000000000003</v>
       </c>
       <c r="G104">
         <v>1365</v>
@@ -9814,7 +9814,7 @@
         <v>127</v>
       </c>
       <c r="F105">
-        <v>0.38325000000000004</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="G105">
         <v>1365</v>
@@ -9876,7 +9876,7 @@
         <v>63</v>
       </c>
       <c r="F106">
-        <v>0.370475</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G106">
         <v>1365</v>
@@ -9938,7 +9938,7 @@
         <v>60</v>
       </c>
       <c r="F107">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="G107">
         <v>1365</v>
@@ -10000,7 +10000,7 @@
         <v>81</v>
       </c>
       <c r="F108">
-        <v>0.33214999999999995</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G108">
         <v>1365</v>
@@ -10062,7 +10062,7 @@
         <v>172</v>
       </c>
       <c r="F109">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G109">
         <v>1365</v>
@@ -10124,7 +10124,7 @@
         <v>174</v>
       </c>
       <c r="F110">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G110">
         <v>1365</v>
@@ -10186,7 +10186,7 @@
         <v>176</v>
       </c>
       <c r="F111">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G111">
         <v>1365</v>
@@ -10248,7 +10248,7 @@
         <v>178</v>
       </c>
       <c r="F112">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="G112">
         <v>1365</v>
@@ -10310,7 +10310,7 @@
         <v>99</v>
       </c>
       <c r="F113">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G113">
         <v>1365</v>
@@ -10372,7 +10372,7 @@
         <v>88</v>
       </c>
       <c r="F114">
-        <v>0.37047499999999994</v>
+        <v>0.30957499999999993</v>
       </c>
       <c r="G114">
         <v>1365</v>
@@ -10434,7 +10434,7 @@
         <v>157</v>
       </c>
       <c r="F115">
-        <v>0.24272499999999997</v>
+        <v>0.20282499999999998</v>
       </c>
       <c r="G115">
         <v>1365</v>
@@ -10496,7 +10496,7 @@
         <v>183</v>
       </c>
       <c r="F116">
-        <v>0.35770000000000002</v>
+        <v>0.29890000000000005</v>
       </c>
       <c r="G116">
         <v>1365</v>
@@ -10558,7 +10558,7 @@
         <v>75</v>
       </c>
       <c r="F117">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="G117">
         <v>1365</v>
@@ -10620,7 +10620,7 @@
         <v>111</v>
       </c>
       <c r="F118">
-        <v>0.35770000000000002</v>
+        <v>0.2989</v>
       </c>
       <c r="G118">
         <v>1365</v>
@@ -10682,7 +10682,7 @@
         <v>187</v>
       </c>
       <c r="F119">
-        <v>0.33215000000000006</v>
+        <v>0.27754999999999996</v>
       </c>
       <c r="G119">
         <v>1365</v>
@@ -10744,7 +10744,7 @@
         <v>115</v>
       </c>
       <c r="F120">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="G120">
         <v>1365</v>
@@ -10806,7 +10806,7 @@
         <v>190</v>
       </c>
       <c r="F121">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G121">
         <v>1365</v>
@@ -10868,7 +10868,7 @@
         <v>190</v>
       </c>
       <c r="F122">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G122">
         <v>1365</v>
@@ -10930,7 +10930,7 @@
         <v>193</v>
       </c>
       <c r="F123">
-        <v>0.16288125000000001</v>
+        <v>0.13610624999999998</v>
       </c>
       <c r="G123">
         <v>1365</v>
@@ -10992,7 +10992,7 @@
         <v>174</v>
       </c>
       <c r="F124">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G124">
         <v>1365</v>
@@ -11054,7 +11054,7 @@
         <v>88</v>
       </c>
       <c r="F125">
-        <v>0.16926875000000002</v>
+        <v>0.14144375000000001</v>
       </c>
       <c r="G125">
         <v>1365</v>
@@ -11116,7 +11116,7 @@
         <v>183</v>
       </c>
       <c r="F126">
-        <v>0.18523749999999997</v>
+        <v>0.15478749999999997</v>
       </c>
       <c r="G126">
         <v>1365</v>
@@ -11178,7 +11178,7 @@
         <v>127</v>
       </c>
       <c r="F127">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G127">
         <v>1365</v>
@@ -11240,7 +11240,7 @@
         <v>199</v>
       </c>
       <c r="F128">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="G128">
         <v>1365</v>
@@ -11302,7 +11302,7 @@
         <v>201</v>
       </c>
       <c r="F129">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G129">
         <v>1365</v>
@@ -11364,7 +11364,7 @@
         <v>157</v>
       </c>
       <c r="F130">
-        <v>0.22994999999999999</v>
+        <v>0.19214999999999999</v>
       </c>
       <c r="G130">
         <v>1365</v>
@@ -11426,7 +11426,7 @@
         <v>88</v>
       </c>
       <c r="F131">
-        <v>0.22994999999999999</v>
+        <v>0.19214999999999999</v>
       </c>
       <c r="G131">
         <v>1365</v>
@@ -11488,7 +11488,7 @@
         <v>91</v>
       </c>
       <c r="F132">
-        <v>0.22675624999999999</v>
+        <v>0.18948125000000002</v>
       </c>
       <c r="G132">
         <v>1365</v>
@@ -11550,7 +11550,7 @@
         <v>206</v>
       </c>
       <c r="F133">
-        <v>0.22994999999999999</v>
+        <v>0.19214999999999999</v>
       </c>
       <c r="G133">
         <v>1365</v>
@@ -11612,7 +11612,7 @@
         <v>88</v>
       </c>
       <c r="F134">
-        <v>0.22994999999999999</v>
+        <v>0.19214999999999999</v>
       </c>
       <c r="G134">
         <v>1365</v>
@@ -11674,7 +11674,7 @@
         <v>187</v>
       </c>
       <c r="F135">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="G135">
         <v>1365</v>
@@ -11736,7 +11736,7 @@
         <v>113</v>
       </c>
       <c r="F136">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G136">
         <v>1365</v>
@@ -11798,7 +11798,7 @@
         <v>85</v>
       </c>
       <c r="F137">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G137">
         <v>1365</v>
@@ -11860,7 +11860,7 @@
         <v>85</v>
       </c>
       <c r="F138">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G138">
         <v>1365</v>
@@ -11922,7 +11922,7 @@
         <v>213</v>
       </c>
       <c r="F139">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="G139">
         <v>1365</v>
@@ -11984,7 +11984,7 @@
         <v>113</v>
       </c>
       <c r="F140">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G140">
         <v>1365</v>
@@ -12046,7 +12046,7 @@
         <v>85</v>
       </c>
       <c r="F141">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="G141">
         <v>1365</v>
@@ -12108,7 +12108,7 @@
         <v>85</v>
       </c>
       <c r="F142">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="G142">
         <v>1365</v>
@@ -12170,7 +12170,7 @@
         <v>176</v>
       </c>
       <c r="F143">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G143">
         <v>1365</v>
@@ -12232,7 +12232,7 @@
         <v>176</v>
       </c>
       <c r="F144">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G144">
         <v>1365</v>
@@ -12294,7 +12294,7 @@
         <v>220</v>
       </c>
       <c r="F145">
-        <v>0.21717500000000001</v>
+        <v>0.18147499999999997</v>
       </c>
       <c r="G145">
         <v>1365</v>
@@ -12356,7 +12356,7 @@
         <v>138</v>
       </c>
       <c r="F146">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G146">
         <v>1365</v>
@@ -12418,7 +12418,7 @@
         <v>60</v>
       </c>
       <c r="F147">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="G147">
         <v>1365</v>
@@ -12480,7 +12480,7 @@
         <v>28</v>
       </c>
       <c r="F148">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G148">
         <v>1365</v>
@@ -12542,7 +12542,7 @@
         <v>206</v>
       </c>
       <c r="F149">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="G149">
         <v>1365</v>
@@ -12604,7 +12604,7 @@
         <v>226</v>
       </c>
       <c r="F150">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G150">
         <v>1365</v>
@@ -12666,7 +12666,7 @@
         <v>199</v>
       </c>
       <c r="F151">
-        <v>0.21078749999999999</v>
+        <v>0.1761375</v>
       </c>
       <c r="G151">
         <v>1365</v>
@@ -12728,7 +12728,7 @@
         <v>34</v>
       </c>
       <c r="F152">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G152">
         <v>1365</v>
@@ -12790,7 +12790,7 @@
         <v>230</v>
       </c>
       <c r="F153">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G153">
         <v>1365</v>
@@ -12852,7 +12852,7 @@
         <v>77</v>
       </c>
       <c r="F154">
-        <v>0.21717499999999998</v>
+        <v>0.181475</v>
       </c>
       <c r="G154">
         <v>1365</v>
@@ -12914,7 +12914,7 @@
         <v>233</v>
       </c>
       <c r="F155">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G155">
         <v>1365</v>
@@ -13224,7 +13224,7 @@
         <v>31</v>
       </c>
       <c r="F160">
-        <v>0.31937500000000002</v>
+        <v>0.26687499999999997</v>
       </c>
       <c r="G160">
         <v>1365</v>
@@ -13286,7 +13286,7 @@
         <v>132</v>
       </c>
       <c r="F161">
-        <v>0.15329999999999999</v>
+        <v>0.12809999999999999</v>
       </c>
       <c r="G161">
         <v>1365</v>
@@ -13348,7 +13348,7 @@
         <v>28</v>
       </c>
       <c r="F162">
-        <v>0.20440000000000003</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="G162">
         <v>1365</v>
@@ -13410,7 +13410,7 @@
         <v>106</v>
       </c>
       <c r="F163">
-        <v>0.21078749999999999</v>
+        <v>0.1761375</v>
       </c>
       <c r="G163">
         <v>1365</v>
@@ -13472,7 +13472,7 @@
         <v>106</v>
       </c>
       <c r="F164">
-        <v>0.21078749999999999</v>
+        <v>0.1761375</v>
       </c>
       <c r="G164">
         <v>1365</v>
@@ -13534,7 +13534,7 @@
         <v>123</v>
       </c>
       <c r="F165">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G165">
         <v>1365</v>
@@ -13596,7 +13596,7 @@
         <v>123</v>
       </c>
       <c r="F166">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G166">
         <v>1365</v>
@@ -13658,7 +13658,7 @@
         <v>123</v>
       </c>
       <c r="F167">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G167">
         <v>1365</v>
@@ -13720,7 +13720,7 @@
         <v>123</v>
       </c>
       <c r="F168">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G168">
         <v>1365</v>
@@ -13782,7 +13782,7 @@
         <v>123</v>
       </c>
       <c r="F169">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G169">
         <v>1365</v>
@@ -13844,7 +13844,7 @@
         <v>123</v>
       </c>
       <c r="F170">
-        <v>0.21717500000000001</v>
+        <v>0.181475</v>
       </c>
       <c r="G170">
         <v>1365</v>
@@ -13906,7 +13906,7 @@
         <v>96</v>
       </c>
       <c r="F171">
-        <v>0.19162500000000002</v>
+        <v>0.16012499999999999</v>
       </c>
       <c r="G171">
         <v>1365</v>
@@ -13968,7 +13968,7 @@
         <v>88</v>
       </c>
       <c r="F172">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G172">
         <v>1365</v>
@@ -14030,7 +14030,7 @@
         <v>157</v>
       </c>
       <c r="F173">
-        <v>0.20439999999999997</v>
+        <v>0.17080000000000001</v>
       </c>
       <c r="G173">
         <v>1365</v>
@@ -14092,7 +14092,7 @@
         <v>213</v>
       </c>
       <c r="F174">
-        <v>0.19162499999999999</v>
+        <v>0.16012499999999999</v>
       </c>
       <c r="G174">
         <v>1365</v>
@@ -14154,7 +14154,7 @@
         <v>199</v>
       </c>
       <c r="F175">
-        <v>0.19162500000000002</v>
+        <v>0.16012499999999999</v>
       </c>
       <c r="G175">
         <v>1365</v>
@@ -14216,7 +14216,7 @@
         <v>132</v>
       </c>
       <c r="F176">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G176">
         <v>1365</v>
@@ -14278,7 +14278,7 @@
         <v>77</v>
       </c>
       <c r="F177">
-        <v>0.19801250000000001</v>
+        <v>0.16546250000000001</v>
       </c>
       <c r="G177">
         <v>1365</v>
@@ -14332,7 +14332,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FDD36C-F7D3-4E29-A219-6AD47B104455}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1418F312-DC41-46E8-BA43-0688972AE049}">
   <dimension ref="B9:V81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18787,7 +18787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C486577-A89B-4EC5-9892-905451529A0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65B57EF4-F622-4D5C-AE6C-987F253AD351}">
   <dimension ref="B9:V441"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18881,7 +18881,7 @@
         <v>0.05</v>
       </c>
       <c r="H11">
-        <v>0.21899999999999997</v>
+        <v>0.183</v>
       </c>
       <c r="I11">
         <v>4725</v>
@@ -18940,7 +18940,7 @@
         <v>0.1122093157894737</v>
       </c>
       <c r="H12">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I12">
         <v>4025</v>
@@ -18999,7 +18999,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="H13">
-        <v>0.219</v>
+        <v>0.18300000000000002</v>
       </c>
       <c r="I13">
         <v>4725</v>
@@ -19058,7 +19058,7 @@
         <v>7.4300763157894759E-2</v>
       </c>
       <c r="H14">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I14">
         <v>4025</v>
@@ -19117,7 +19117,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="H15">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="I15">
         <v>4725</v>
@@ -19176,7 +19176,7 @@
         <v>6.823539473684212E-2</v>
       </c>
       <c r="H16">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I16">
         <v>4024.9999999999991</v>
@@ -19235,7 +19235,7 @@
         <v>0.04</v>
       </c>
       <c r="H17">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="I17">
         <v>4725</v>
@@ -19294,7 +19294,7 @@
         <v>0.13647078947368424</v>
       </c>
       <c r="H18">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I18">
         <v>4024.9999999999991</v>
@@ -19353,7 +19353,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="H19">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="I19">
         <v>4725</v>
@@ -19412,7 +19412,7 @@
         <v>5.0039289473684231E-2</v>
       </c>
       <c r="H20">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I20">
         <v>4024.9999999999995</v>
@@ -19471,7 +19471,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="H21">
-        <v>0.219</v>
+        <v>0.18300000000000002</v>
       </c>
       <c r="I21">
         <v>4725</v>
@@ -19530,7 +19530,7 @@
         <v>7.4300763157894759E-2</v>
       </c>
       <c r="H22">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I22">
         <v>4025</v>
@@ -19589,7 +19589,7 @@
         <v>0.04</v>
       </c>
       <c r="H23">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="I23">
         <v>4725</v>
@@ -19648,7 +19648,7 @@
         <v>6.0653684210526325E-2</v>
       </c>
       <c r="H24">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I24">
         <v>4024.9999999999995</v>
@@ -19707,7 +19707,7 @@
         <v>1.9999999999997797E-3</v>
       </c>
       <c r="H25">
-        <v>0.24179790000000001</v>
+        <v>0.20205030000000002</v>
       </c>
       <c r="L25">
         <v>33</v>
@@ -19757,7 +19757,7 @@
         <v>0.3</v>
       </c>
       <c r="H26">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I26">
         <v>2300</v>
@@ -19816,7 +19816,7 @@
         <v>0.3</v>
       </c>
       <c r="H27">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I27">
         <v>2300</v>
@@ -19875,7 +19875,7 @@
         <v>0.3</v>
       </c>
       <c r="H28">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I28">
         <v>2300</v>
@@ -19934,7 +19934,7 @@
         <v>0.3</v>
       </c>
       <c r="H29">
-        <v>0.24089999999999998</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I29">
         <v>2300</v>
@@ -19993,7 +19993,7 @@
         <v>0.35</v>
       </c>
       <c r="H30">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I30">
         <v>2000</v>
@@ -20052,7 +20052,7 @@
         <v>0.35</v>
       </c>
       <c r="H31">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I31">
         <v>2000</v>
@@ -20111,7 +20111,7 @@
         <v>0.35</v>
       </c>
       <c r="H32">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I32">
         <v>2000</v>
@@ -20170,7 +20170,7 @@
         <v>0.35</v>
       </c>
       <c r="H33">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I33">
         <v>2000</v>
@@ -20229,7 +20229,7 @@
         <v>0.35</v>
       </c>
       <c r="H34">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I34">
         <v>2000</v>
@@ -20288,7 +20288,7 @@
         <v>0.35</v>
       </c>
       <c r="H35">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I35">
         <v>2000</v>
@@ -20347,7 +20347,7 @@
         <v>0.35</v>
       </c>
       <c r="H36">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I36">
         <v>2000</v>
@@ -20406,7 +20406,7 @@
         <v>0.35</v>
       </c>
       <c r="H37">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I37">
         <v>2000</v>
@@ -20465,7 +20465,7 @@
         <v>0.35</v>
       </c>
       <c r="H38">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I38">
         <v>2000</v>
@@ -20524,7 +20524,7 @@
         <v>0.35</v>
       </c>
       <c r="H39">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I39">
         <v>2000</v>
@@ -20583,7 +20583,7 @@
         <v>0.67800000000000005</v>
       </c>
       <c r="H40">
-        <v>0.28835</v>
+        <v>0.24095</v>
       </c>
       <c r="I40">
         <v>2200</v>
@@ -20642,7 +20642,7 @@
         <v>0.51400000000000001</v>
       </c>
       <c r="H41">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I41">
         <v>1000</v>
@@ -20701,7 +20701,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="H42">
-        <v>0.42339999999999989</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I42">
         <v>1000</v>
@@ -20760,7 +20760,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="H43">
-        <v>0.42339999999999989</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I43">
         <v>1000</v>
@@ -20819,7 +20819,7 @@
         <v>0.45850000000000002</v>
       </c>
       <c r="H44">
-        <v>0.4234</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I44">
         <v>1000</v>
@@ -20878,7 +20878,7 @@
         <v>0.874</v>
       </c>
       <c r="H45">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I45">
         <v>1000</v>
@@ -20937,7 +20937,7 @@
         <v>0.86599999999999999</v>
       </c>
       <c r="H46">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I46">
         <v>1000</v>
@@ -20996,7 +20996,7 @@
         <v>0.878</v>
       </c>
       <c r="H47">
-        <v>0.42339999999999994</v>
+        <v>0.3538</v>
       </c>
       <c r="I47">
         <v>1000</v>
@@ -21055,7 +21055,7 @@
         <v>0.85</v>
       </c>
       <c r="H48">
-        <v>0.438</v>
+        <v>0.36599999999999994</v>
       </c>
       <c r="I48">
         <v>1000</v>
@@ -21114,7 +21114,7 @@
         <v>0.76600000000000001</v>
       </c>
       <c r="H49">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I49">
         <v>1000</v>
@@ -21173,7 +21173,7 @@
         <v>0.39300000000000002</v>
       </c>
       <c r="H50">
-        <v>0.42339999999999989</v>
+        <v>0.3538</v>
       </c>
       <c r="I50">
         <v>1000</v>
@@ -21232,7 +21232,7 @@
         <v>0.35</v>
       </c>
       <c r="H51">
-        <v>0.42339999999999989</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I51">
         <v>1000</v>
@@ -21291,7 +21291,7 @@
         <v>0.433</v>
       </c>
       <c r="H52">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I52">
         <v>1000</v>
@@ -21350,7 +21350,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="H53">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I53">
         <v>1000</v>
@@ -21409,7 +21409,7 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="H54">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I54">
         <v>1000</v>
@@ -21468,7 +21468,7 @@
         <v>0.2581</v>
       </c>
       <c r="H55">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I55">
         <v>1150</v>
@@ -21527,7 +21527,7 @@
         <v>0.2581</v>
       </c>
       <c r="H56">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I56">
         <v>1150</v>
@@ -21586,7 +21586,7 @@
         <v>0.72699999999999998</v>
       </c>
       <c r="H57">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I57">
         <v>1000</v>
@@ -21645,7 +21645,7 @@
         <v>0.72699999999999998</v>
       </c>
       <c r="H58">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I58">
         <v>1000</v>
@@ -21704,7 +21704,7 @@
         <v>1.0680000000000001</v>
       </c>
       <c r="H59">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I59">
         <v>1000</v>
@@ -21763,7 +21763,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="H60">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I60">
         <v>1000</v>
@@ -21822,7 +21822,7 @@
         <v>0.45900000000000002</v>
       </c>
       <c r="H61">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="I61">
         <v>1000</v>
@@ -21881,7 +21881,7 @@
         <v>0.378</v>
       </c>
       <c r="H62">
-        <v>0.32850000000000001</v>
+        <v>0.27450000000000002</v>
       </c>
       <c r="I62">
         <v>1000</v>
@@ -21940,7 +21940,7 @@
         <v>0.76879999999999993</v>
       </c>
       <c r="H63">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I63">
         <v>1000.0000000000001</v>
@@ -21999,7 +21999,7 @@
         <v>0.25</v>
       </c>
       <c r="H64">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I64">
         <v>1150</v>
@@ -22058,7 +22058,7 @@
         <v>0.79100000000000004</v>
       </c>
       <c r="H65">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999989</v>
       </c>
       <c r="I65">
         <v>1000</v>
@@ -22117,7 +22117,7 @@
         <v>0.77</v>
       </c>
       <c r="H66">
-        <v>0.42339999999999994</v>
+        <v>0.3538</v>
       </c>
       <c r="I66">
         <v>1000</v>
@@ -22176,7 +22176,7 @@
         <v>0.38600000000000001</v>
       </c>
       <c r="H67">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I67">
         <v>1000</v>
@@ -22235,7 +22235,7 @@
         <v>0.61899999999999999</v>
       </c>
       <c r="H68">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I68">
         <v>1000</v>
@@ -22294,7 +22294,7 @@
         <v>0.32700000000000001</v>
       </c>
       <c r="H69">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I69">
         <v>1000</v>
@@ -22353,7 +22353,7 @@
         <v>0.72799999999999998</v>
       </c>
       <c r="H70">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I70">
         <v>1000</v>
@@ -22412,7 +22412,7 @@
         <v>0.76970000000000005</v>
       </c>
       <c r="H71">
-        <v>0.438</v>
+        <v>0.36599999999999994</v>
       </c>
       <c r="I71">
         <v>999.99999999999989</v>
@@ -22471,7 +22471,7 @@
         <v>0.45539999999999997</v>
       </c>
       <c r="H72">
-        <v>0.438</v>
+        <v>0.36600000000000005</v>
       </c>
       <c r="I72">
         <v>1000</v>
@@ -22530,7 +22530,7 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="H73">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I73">
         <v>1150</v>
@@ -22589,7 +22589,7 @@
         <v>0.38200000000000001</v>
       </c>
       <c r="H74">
-        <v>0.39784999999999998</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I74">
         <v>1000</v>
@@ -22648,7 +22648,7 @@
         <v>0.2475</v>
       </c>
       <c r="H75">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I75">
         <v>1150</v>
@@ -22707,7 +22707,7 @@
         <v>0.93240000000000001</v>
       </c>
       <c r="H76">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I76">
         <v>1000</v>
@@ -22766,7 +22766,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="H77">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I77">
         <v>1000</v>
@@ -22825,7 +22825,7 @@
         <v>1.1319000000000001</v>
       </c>
       <c r="H78">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I78">
         <v>999.99999999999989</v>
@@ -22884,7 +22884,7 @@
         <v>0.495</v>
       </c>
       <c r="H79">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I79">
         <v>1000</v>
@@ -22943,7 +22943,7 @@
         <v>0.59</v>
       </c>
       <c r="H80">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I80">
         <v>1000</v>
@@ -23002,7 +23002,7 @@
         <v>0.59</v>
       </c>
       <c r="H81">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I81">
         <v>1000</v>
@@ -23061,7 +23061,7 @@
         <v>0.495</v>
       </c>
       <c r="H82">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I82">
         <v>1000</v>
@@ -23120,7 +23120,7 @@
         <v>1.1513</v>
       </c>
       <c r="H83">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I83">
         <v>1000</v>
@@ -23179,7 +23179,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="H84">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I84">
         <v>1150</v>
@@ -23238,7 +23238,7 @@
         <v>0.36260000000000003</v>
       </c>
       <c r="H85">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="I85">
         <v>999.99999999999989</v>
@@ -23297,7 +23297,7 @@
         <v>0.9</v>
       </c>
       <c r="H86">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I86">
         <v>1000</v>
@@ -23356,7 +23356,7 @@
         <v>0.26600000000000001</v>
       </c>
       <c r="H87">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I87">
         <v>1150</v>
@@ -23415,7 +23415,7 @@
         <v>0.505</v>
       </c>
       <c r="H88">
-        <v>0.38324999999999998</v>
+        <v>0.32024999999999998</v>
       </c>
       <c r="I88">
         <v>1000</v>
@@ -23474,7 +23474,7 @@
         <v>0.5</v>
       </c>
       <c r="H89">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I89">
         <v>1000</v>
@@ -23533,7 +23533,7 @@
         <v>0.495</v>
       </c>
       <c r="H90">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I90">
         <v>1000</v>
@@ -23592,7 +23592,7 @@
         <v>0.495</v>
       </c>
       <c r="H91">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I91">
         <v>1000</v>
@@ -23651,7 +23651,7 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="H92">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I92">
         <v>1000</v>
@@ -23710,7 +23710,7 @@
         <v>0.54900000000000004</v>
       </c>
       <c r="H93">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I93">
         <v>1000</v>
@@ -23769,7 +23769,7 @@
         <v>0.56459999999999999</v>
       </c>
       <c r="H94">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I94">
         <v>1000</v>
@@ -23828,7 +23828,7 @@
         <v>0.252</v>
       </c>
       <c r="H95">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I95">
         <v>1150</v>
@@ -23887,7 +23887,7 @@
         <v>0.252</v>
       </c>
       <c r="H96">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I96">
         <v>1150</v>
@@ -23946,7 +23946,7 @@
         <v>0.65600000000000003</v>
       </c>
       <c r="H97">
-        <v>0.43799999999999994</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I97">
         <v>1000</v>
@@ -24005,7 +24005,7 @@
         <v>0.32400000000000001</v>
       </c>
       <c r="H98">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I98">
         <v>1000</v>
@@ -24064,7 +24064,7 @@
         <v>0.57699999999999996</v>
       </c>
       <c r="H99">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I99">
         <v>1000</v>
@@ -24123,7 +24123,7 @@
         <v>0.57799999999999996</v>
       </c>
       <c r="H100">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I100">
         <v>1000</v>
@@ -24182,7 +24182,7 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="H101">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I101">
         <v>1000</v>
@@ -24241,7 +24241,7 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="H102">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I102">
         <v>1000</v>
@@ -24300,7 +24300,7 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="H103">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I103">
         <v>1000</v>
@@ -24359,7 +24359,7 @@
         <v>0.3</v>
       </c>
       <c r="H104">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I104">
         <v>1150</v>
@@ -24418,7 +24418,7 @@
         <v>0.252</v>
       </c>
       <c r="H105">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I105">
         <v>1150</v>
@@ -24477,7 +24477,7 @@
         <v>0.252</v>
       </c>
       <c r="H106">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I106">
         <v>1150</v>
@@ -24536,7 +24536,7 @@
         <v>0.58950000000000002</v>
       </c>
       <c r="H107">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I107">
         <v>1000</v>
@@ -24595,7 +24595,7 @@
         <v>0.58950000000000002</v>
       </c>
       <c r="H108">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I108">
         <v>1000</v>
@@ -24654,7 +24654,7 @@
         <v>0.53700000000000003</v>
       </c>
       <c r="H109">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I109">
         <v>1000</v>
@@ -24713,7 +24713,7 @@
         <v>0.625</v>
       </c>
       <c r="H110">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I110">
         <v>1000</v>
@@ -24772,7 +24772,7 @@
         <v>0.495</v>
       </c>
       <c r="H111">
-        <v>0.39785000000000004</v>
+        <v>0.33245000000000002</v>
       </c>
       <c r="I111">
         <v>1000</v>
@@ -24831,7 +24831,7 @@
         <v>0.27789999999999998</v>
       </c>
       <c r="H112">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I112">
         <v>1150</v>
@@ -24890,7 +24890,7 @@
         <v>0.28299999999999997</v>
       </c>
       <c r="H113">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I113">
         <v>1150</v>
@@ -24949,7 +24949,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="H114">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I114">
         <v>1150</v>
@@ -25008,7 +25008,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="H115">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I115">
         <v>1150</v>
@@ -25067,7 +25067,7 @@
         <v>0.248</v>
       </c>
       <c r="H116">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I116">
         <v>1150</v>
@@ -25126,7 +25126,7 @@
         <v>0.26200000000000001</v>
       </c>
       <c r="H117">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I117">
         <v>1150</v>
@@ -25185,7 +25185,7 @@
         <v>0.37139999999999995</v>
       </c>
       <c r="H118">
-        <v>0.438</v>
+        <v>0.36600000000000005</v>
       </c>
       <c r="I118">
         <v>1000.0000000000001</v>
@@ -25244,7 +25244,7 @@
         <v>0.34100000000000003</v>
       </c>
       <c r="H119">
-        <v>0.438</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="I119">
         <v>1000</v>
@@ -25303,7 +25303,7 @@
         <v>0.45850000000000002</v>
       </c>
       <c r="H120">
-        <v>0.4234</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I120">
         <v>1000</v>
@@ -25362,7 +25362,7 @@
         <v>0.52200000000000002</v>
       </c>
       <c r="H121">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I121">
         <v>1150</v>
@@ -25421,7 +25421,7 @@
         <v>0.22700000000000001</v>
       </c>
       <c r="H122">
-        <v>0.37959999999999999</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I122">
         <v>1150</v>
@@ -25480,7 +25480,7 @@
         <v>0.23200000000000001</v>
       </c>
       <c r="H123">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I123">
         <v>1150</v>
@@ -25539,7 +25539,7 @@
         <v>0.33550000000000002</v>
       </c>
       <c r="H124">
-        <v>0.36500000000000005</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I124">
         <v>1150</v>
@@ -25598,7 +25598,7 @@
         <v>0.17560000000000001</v>
       </c>
       <c r="H125">
-        <v>0.4088</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I125">
         <v>1150</v>
@@ -25657,7 +25657,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H126">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I126">
         <v>1150</v>
@@ -25716,7 +25716,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="H127">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I127">
         <v>1150</v>
@@ -25775,7 +25775,7 @@
         <v>0.45200000000000001</v>
       </c>
       <c r="H128">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I128">
         <v>1150</v>
@@ -25834,7 +25834,7 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="H129">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I129">
         <v>1150</v>
@@ -25893,7 +25893,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="H130">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I130">
         <v>1150</v>
@@ -25952,7 +25952,7 @@
         <v>0.15</v>
       </c>
       <c r="H131">
-        <v>0.42339999999999994</v>
+        <v>0.35379999999999995</v>
       </c>
       <c r="I131">
         <v>1150</v>
@@ -26011,7 +26011,7 @@
         <v>0.23980000000000001</v>
       </c>
       <c r="H132">
-        <v>0.27739999999999998</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="I132">
         <v>1150</v>
@@ -26070,7 +26070,7 @@
         <v>0.11799999999999999</v>
       </c>
       <c r="H133">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000007</v>
       </c>
       <c r="I133">
         <v>1150</v>
@@ -26129,7 +26129,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="H134">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I134">
         <v>1150</v>
@@ -26188,7 +26188,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="H135">
-        <v>0.40880000000000005</v>
+        <v>0.34160000000000001</v>
       </c>
       <c r="I135">
         <v>1150</v>
@@ -26247,7 +26247,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="H136">
-        <v>0.37960000000000005</v>
+        <v>0.31719999999999998</v>
       </c>
       <c r="I136">
         <v>1150</v>
@@ -26306,7 +26306,7 @@
         <v>0.22</v>
       </c>
       <c r="H137">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I137">
         <v>1150</v>
@@ -26365,7 +26365,7 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="H138">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I138">
         <v>919.99999999999989</v>
@@ -26424,7 +26424,7 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="H139">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I139">
         <v>919.99999999999989</v>
@@ -26483,7 +26483,7 @@
         <v>0.05</v>
       </c>
       <c r="H140">
-        <v>0.18615000000000001</v>
+        <v>0.15554999999999999</v>
       </c>
       <c r="I140">
         <v>1080</v>
@@ -26542,7 +26542,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="H141">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I141">
         <v>919.99999999999989</v>
@@ -26601,7 +26601,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="H142">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I142">
         <v>919.99999999999989</v>
@@ -26660,7 +26660,7 @@
         <v>0.17100000000000001</v>
       </c>
       <c r="H143">
-        <v>0.19345000000000001</v>
+        <v>0.16165000000000002</v>
       </c>
       <c r="I143">
         <v>919.99999999999989</v>
@@ -26719,7 +26719,7 @@
         <v>5.96E-2</v>
       </c>
       <c r="H144">
-        <v>0.21169999999999997</v>
+        <v>0.17689999999999997</v>
       </c>
       <c r="I144">
         <v>919.99999999999989</v>
@@ -26778,7 +26778,7 @@
         <v>0.3</v>
       </c>
       <c r="H145">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I145">
         <v>919.99999999999977</v>
@@ -26837,7 +26837,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="H146">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="I146">
         <v>919.99999999999989</v>
@@ -26896,7 +26896,7 @@
         <v>0.2</v>
       </c>
       <c r="H147">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I147">
         <v>919.99999999999989</v>
@@ -26955,7 +26955,7 @@
         <v>0.3634</v>
       </c>
       <c r="H148">
-        <v>0.26279999999999998</v>
+        <v>0.21960000000000002</v>
       </c>
       <c r="I148">
         <v>1100</v>
@@ -27014,7 +27014,7 @@
         <v>0.44160000000000005</v>
       </c>
       <c r="H149">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I149">
         <v>1100</v>
@@ -27073,7 +27073,7 @@
         <v>0.13090000000000002</v>
       </c>
       <c r="H150">
-        <v>0.25914999999999999</v>
+        <v>0.21654999999999999</v>
       </c>
       <c r="I150">
         <v>1265</v>
@@ -27132,7 +27132,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="H151">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I151">
         <v>1265</v>
@@ -27191,7 +27191,7 @@
         <v>0.22</v>
       </c>
       <c r="H152">
-        <v>0.26279999999999998</v>
+        <v>0.21959999999999999</v>
       </c>
       <c r="I152">
         <v>1265</v>
@@ -27250,7 +27250,7 @@
         <v>0.3</v>
       </c>
       <c r="H153">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="I153">
         <v>1380</v>
@@ -27309,7 +27309,7 @@
         <v>0.3</v>
       </c>
       <c r="H154">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I154">
         <v>1380</v>
@@ -27368,7 +27368,7 @@
         <v>0.35</v>
       </c>
       <c r="H155">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I155">
         <v>1200</v>
@@ -27427,7 +27427,7 @@
         <v>0.35</v>
       </c>
       <c r="H156">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I156">
         <v>1200</v>
@@ -27486,7 +27486,7 @@
         <v>0.3</v>
       </c>
       <c r="H157">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="I157">
         <v>1380</v>
@@ -27545,7 +27545,7 @@
         <v>0.25</v>
       </c>
       <c r="H158">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I158">
         <v>1380</v>
@@ -27604,7 +27604,7 @@
         <v>0.3</v>
       </c>
       <c r="H159">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="I159">
         <v>1380</v>
@@ -27663,7 +27663,7 @@
         <v>0.3</v>
       </c>
       <c r="H160">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="I160">
         <v>1380</v>
@@ -27722,7 +27722,7 @@
         <v>0.25</v>
       </c>
       <c r="H161">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I161">
         <v>1380</v>
@@ -27781,7 +27781,7 @@
         <v>0.25</v>
       </c>
       <c r="H162">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I162">
         <v>1380</v>
@@ -27840,7 +27840,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="H163">
-        <v>0.2482</v>
+        <v>0.20739999999999997</v>
       </c>
       <c r="I163">
         <v>1380</v>
@@ -27899,7 +27899,7 @@
         <v>0.15</v>
       </c>
       <c r="H164">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="I164">
         <v>1380</v>
@@ -27958,7 +27958,7 @@
         <v>0.15</v>
       </c>
       <c r="H165">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I165">
         <v>1380</v>
@@ -28017,7 +28017,7 @@
         <v>0.316</v>
       </c>
       <c r="H166">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="I166">
         <v>1380</v>
@@ -28076,7 +28076,7 @@
         <v>0.13369999999999999</v>
       </c>
       <c r="H167">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I167">
         <v>1380</v>
@@ -28135,7 +28135,7 @@
         <v>0.63200000000000001</v>
       </c>
       <c r="H168">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="I168">
         <v>1380</v>
@@ -28194,7 +28194,7 @@
         <v>0.115</v>
       </c>
       <c r="H169">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I169">
         <v>1380</v>
@@ -28253,7 +28253,7 @@
         <v>0.32</v>
       </c>
       <c r="H170">
-        <v>0.24089999999999998</v>
+        <v>0.20129999999999998</v>
       </c>
       <c r="I170">
         <v>1380</v>
@@ -28312,7 +28312,7 @@
         <v>0.129</v>
       </c>
       <c r="H171">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I171">
         <v>1380</v>
@@ -28371,7 +28371,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="H172">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I172">
         <v>1380</v>
@@ -28430,7 +28430,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="H173">
-        <v>0.24819999999999998</v>
+        <v>0.2074</v>
       </c>
       <c r="I173">
         <v>1380</v>
@@ -28489,7 +28489,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="H174">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I174">
         <v>1380</v>
@@ -32873,7 +32873,7 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="H251">
-        <v>0.36499999999999999</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I251">
         <v>1265</v>
@@ -32932,7 +32932,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="H252">
-        <v>0.17519999999999999</v>
+        <v>0.1464</v>
       </c>
       <c r="I252">
         <v>1035</v>
@@ -32991,7 +32991,7 @@
         <v>0.32300000000000001</v>
       </c>
       <c r="H253">
-        <v>0.2336</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="I253">
         <v>1300</v>
@@ -33050,7 +33050,7 @@
         <v>0.35</v>
       </c>
       <c r="H254">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I254">
         <v>1300</v>
@@ -33109,7 +33109,7 @@
         <v>0.35</v>
       </c>
       <c r="H255">
-        <v>0.2409</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="I255">
         <v>1300</v>
@@ -33168,7 +33168,7 @@
         <v>0.35</v>
       </c>
       <c r="H256">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I256">
         <v>1300</v>
@@ -33227,7 +33227,7 @@
         <v>0.35</v>
       </c>
       <c r="H257">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I257">
         <v>1300</v>
@@ -33286,7 +33286,7 @@
         <v>0.35</v>
       </c>
       <c r="H258">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I258">
         <v>1300</v>
@@ -33345,7 +33345,7 @@
         <v>0.35</v>
       </c>
       <c r="H259">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I259">
         <v>1300</v>
@@ -33404,7 +33404,7 @@
         <v>0.35</v>
       </c>
       <c r="H260">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I260">
         <v>1300</v>
@@ -33463,7 +33463,7 @@
         <v>0.35</v>
       </c>
       <c r="H261">
-        <v>0.2482</v>
+        <v>0.2074</v>
       </c>
       <c r="I261">
         <v>1300</v>
@@ -33522,7 +33522,7 @@
         <v>0.48399999999999999</v>
       </c>
       <c r="H262">
-        <v>0.21900000000000003</v>
+        <v>0.183</v>
       </c>
       <c r="I262">
         <v>1494.9999999999998</v>
@@ -33581,7 +33581,7 @@
         <v>0.32</v>
       </c>
       <c r="H263">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I263">
         <v>1494.9999999999998</v>
@@ -33640,7 +33640,7 @@
         <v>0.32</v>
       </c>
       <c r="H264">
-        <v>0.23359999999999997</v>
+        <v>0.19520000000000001</v>
       </c>
       <c r="I264">
         <v>1494.9999999999998</v>
@@ -33699,7 +33699,7 @@
         <v>0.316</v>
       </c>
       <c r="H265">
-        <v>0.21899999999999997</v>
+        <v>0.183</v>
       </c>
       <c r="I265">
         <v>1494.9999999999998</v>
@@ -33758,7 +33758,7 @@
         <v>0.113</v>
       </c>
       <c r="H266">
-        <v>0.219</v>
+        <v>0.183</v>
       </c>
       <c r="I266">
         <v>1494.9999999999998</v>
@@ -33817,7 +33817,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="H267">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I267">
         <v>1494.9999999999998</v>
@@ -33876,7 +33876,7 @@
         <v>0.3</v>
       </c>
       <c r="H268">
-        <v>0.2263</v>
+        <v>0.18909999999999999</v>
       </c>
       <c r="I268">
         <v>1494.9999999999998</v>
@@ -34024,7 +34024,7 @@
         <v>14</v>
       </c>
       <c r="R270" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="S270" t="s">
         <v>498</v>
@@ -34086,7 +34086,7 @@
         <v>14</v>
       </c>
       <c r="R271" t="s">
-        <v>606</v>
+        <v>504</v>
       </c>
       <c r="S271" t="s">
         <v>498</v>
@@ -34272,7 +34272,7 @@
         <v>14</v>
       </c>
       <c r="R274" t="s">
-        <v>606</v>
+        <v>504</v>
       </c>
       <c r="S274" t="s">
         <v>498</v>
@@ -34334,7 +34334,7 @@
         <v>14</v>
       </c>
       <c r="R275" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="S275" t="s">
         <v>498</v>
@@ -38674,7 +38674,7 @@
         <v>14</v>
       </c>
       <c r="R345" t="s">
-        <v>606</v>
+        <v>504</v>
       </c>
       <c r="S345" t="s">
         <v>498</v>
@@ -38736,7 +38736,7 @@
         <v>14</v>
       </c>
       <c r="R346" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="S346" t="s">
         <v>498</v>
@@ -38922,7 +38922,7 @@
         <v>14</v>
       </c>
       <c r="R349" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="S349" t="s">
         <v>498</v>
@@ -38984,7 +38984,7 @@
         <v>14</v>
       </c>
       <c r="R350" t="s">
-        <v>606</v>
+        <v>504</v>
       </c>
       <c r="S350" t="s">
         <v>498</v>
@@ -42775,7 +42775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA9D825-7A1D-40BE-A94A-1713936C77CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C60CC5-BB93-4D53-BD77-6B7EDF959D70}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_MEX_grids_kan/vt_vervestacks_MEX_v1.xlsx
+++ b/VerveStacks_MEX_grids_kan/vt_vervestacks_MEX_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91E28A88-61C1-47BC-8480-19A3A645B0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CAC510B-248D-4CE4-9484-A86479C16936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1A5B4945-F7C3-4342-BF4F-7187E21BB802}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{78F05441-9312-4BBA-92DD-5A328797236F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3898,7 +3898,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C46F0B0-3FA7-4F00-A21F-77C3BEBA6DE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E191B83-5C9E-4A2E-9231-3B785DA47276}">
   <dimension ref="B9:V177"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3986,7 +3986,7 @@
         <v>38</v>
       </c>
       <c r="F11">
-        <v>6.1423291200000014E-2</v>
+        <v>6.6457987200000013E-2</v>
       </c>
       <c r="G11">
         <v>3583</v>
@@ -4048,7 +4048,7 @@
         <v>40</v>
       </c>
       <c r="F12">
-        <v>6.1195200000000012E-2</v>
+        <v>6.6211200000000026E-2</v>
       </c>
       <c r="G12">
         <v>3583</v>
@@ -4110,7 +4110,7 @@
         <v>40</v>
       </c>
       <c r="F13">
-        <v>6.1195200000000012E-2</v>
+        <v>6.6211200000000026E-2</v>
       </c>
       <c r="G13">
         <v>3583</v>
@@ -4172,7 +4172,7 @@
         <v>40</v>
       </c>
       <c r="F14">
-        <v>6.1195200000000012E-2</v>
+        <v>6.6211200000000026E-2</v>
       </c>
       <c r="G14">
         <v>3583</v>
@@ -4234,7 +4234,7 @@
         <v>40</v>
       </c>
       <c r="F15">
-        <v>6.1195200000000012E-2</v>
+        <v>6.6211200000000026E-2</v>
       </c>
       <c r="G15">
         <v>3583</v>
@@ -4296,7 +4296,7 @@
         <v>40</v>
       </c>
       <c r="F16">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G16">
         <v>3583</v>
@@ -4358,7 +4358,7 @@
         <v>40</v>
       </c>
       <c r="F17">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G17">
         <v>3583</v>
@@ -4420,7 +4420,7 @@
         <v>40</v>
       </c>
       <c r="F18">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G18">
         <v>3583</v>
@@ -4482,7 +4482,7 @@
         <v>40</v>
       </c>
       <c r="F19">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G19">
         <v>3583</v>
@@ -4544,7 +4544,7 @@
         <v>49</v>
       </c>
       <c r="F20">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G20">
         <v>3583</v>
@@ -4606,7 +4606,7 @@
         <v>49</v>
       </c>
       <c r="F21">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G21">
         <v>3583</v>
@@ -4668,7 +4668,7 @@
         <v>49</v>
       </c>
       <c r="F22">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G22">
         <v>3583</v>
@@ -4730,7 +4730,7 @@
         <v>49</v>
       </c>
       <c r="F23">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G23">
         <v>3583</v>
@@ -4792,7 +4792,7 @@
         <v>49</v>
       </c>
       <c r="F24">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G24">
         <v>3583</v>
@@ -4854,7 +4854,7 @@
         <v>49</v>
       </c>
       <c r="F25">
-        <v>6.6758400000000009E-2</v>
+        <v>7.2230400000000014E-2</v>
       </c>
       <c r="G25">
         <v>3583</v>
@@ -4916,7 +4916,7 @@
         <v>49</v>
       </c>
       <c r="F26">
-        <v>0.16721930000000002</v>
+        <v>0.18092580000000005</v>
       </c>
       <c r="G26">
         <v>2445</v>
@@ -4978,7 +4978,7 @@
         <v>58</v>
       </c>
       <c r="F27">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G27">
         <v>1365</v>
@@ -5040,7 +5040,7 @@
         <v>60</v>
       </c>
       <c r="F28">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G28">
         <v>1365</v>
@@ -5102,7 +5102,7 @@
         <v>60</v>
       </c>
       <c r="F29">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G29">
         <v>1365</v>
@@ -5164,7 +5164,7 @@
         <v>63</v>
       </c>
       <c r="F30">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999991</v>
       </c>
       <c r="G30">
         <v>1365</v>
@@ -5226,7 +5226,7 @@
         <v>65</v>
       </c>
       <c r="F31">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G31">
         <v>1365</v>
@@ -5288,7 +5288,7 @@
         <v>67</v>
       </c>
       <c r="F32">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G32">
         <v>1365</v>
@@ -5350,7 +5350,7 @@
         <v>67</v>
       </c>
       <c r="F33">
-        <v>0.30957499999999999</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G33">
         <v>1365</v>
@@ -5412,7 +5412,7 @@
         <v>70</v>
       </c>
       <c r="F34">
-        <v>0.32024999999999992</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G34">
         <v>1365</v>
@@ -5474,7 +5474,7 @@
         <v>63</v>
       </c>
       <c r="F35">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G35">
         <v>1365</v>
@@ -5536,7 +5536,7 @@
         <v>73</v>
       </c>
       <c r="F36">
-        <v>0.30957499999999999</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G36">
         <v>1365</v>
@@ -5598,7 +5598,7 @@
         <v>75</v>
       </c>
       <c r="F37">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G37">
         <v>1365</v>
@@ -5660,7 +5660,7 @@
         <v>77</v>
       </c>
       <c r="F38">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G38">
         <v>1365</v>
@@ -5722,7 +5722,7 @@
         <v>79</v>
       </c>
       <c r="F39">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G39">
         <v>1365</v>
@@ -5784,7 +5784,7 @@
         <v>81</v>
       </c>
       <c r="F40">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G40">
         <v>1365</v>
@@ -5846,7 +5846,7 @@
         <v>81</v>
       </c>
       <c r="F41">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G41">
         <v>1365</v>
@@ -5908,7 +5908,7 @@
         <v>81</v>
       </c>
       <c r="F42">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G42">
         <v>1365</v>
@@ -5970,7 +5970,7 @@
         <v>85</v>
       </c>
       <c r="F43">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G43">
         <v>1365</v>
@@ -6032,7 +6032,7 @@
         <v>85</v>
       </c>
       <c r="F44">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G44">
         <v>1365</v>
@@ -6094,7 +6094,7 @@
         <v>88</v>
       </c>
       <c r="F45">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G45">
         <v>1365</v>
@@ -6156,7 +6156,7 @@
         <v>88</v>
       </c>
       <c r="F46">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G46">
         <v>1365</v>
@@ -6218,7 +6218,7 @@
         <v>91</v>
       </c>
       <c r="F47">
-        <v>0.28021874999999996</v>
+        <v>0.3031875</v>
       </c>
       <c r="G47">
         <v>1365</v>
@@ -6280,7 +6280,7 @@
         <v>91</v>
       </c>
       <c r="F48">
-        <v>0.2401875</v>
+        <v>0.25987500000000002</v>
       </c>
       <c r="G48">
         <v>1365</v>
@@ -6342,7 +6342,7 @@
         <v>88</v>
       </c>
       <c r="F49">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G49">
         <v>1365</v>
@@ -6404,7 +6404,7 @@
         <v>81</v>
       </c>
       <c r="F50">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G50">
         <v>1365</v>
@@ -6466,7 +6466,7 @@
         <v>96</v>
       </c>
       <c r="F51">
-        <v>0.30957499999999988</v>
+        <v>0.33494999999999991</v>
       </c>
       <c r="G51">
         <v>1365</v>
@@ -6528,7 +6528,7 @@
         <v>96</v>
       </c>
       <c r="F52">
-        <v>0.30957499999999999</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G52">
         <v>1365</v>
@@ -6590,7 +6590,7 @@
         <v>99</v>
       </c>
       <c r="F53">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G53">
         <v>1365</v>
@@ -6652,7 +6652,7 @@
         <v>77</v>
       </c>
       <c r="F54">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G54">
         <v>1365</v>
@@ -6714,7 +6714,7 @@
         <v>60</v>
       </c>
       <c r="F55">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G55">
         <v>1365</v>
@@ -6776,7 +6776,7 @@
         <v>103</v>
       </c>
       <c r="F56">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G56">
         <v>1365</v>
@@ -6838,7 +6838,7 @@
         <v>88</v>
       </c>
       <c r="F57">
-        <v>0.32024999999999992</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G57">
         <v>1365</v>
@@ -6900,7 +6900,7 @@
         <v>106</v>
       </c>
       <c r="F58">
-        <v>0.32025000000000003</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G58">
         <v>1365</v>
@@ -6962,7 +6962,7 @@
         <v>103</v>
       </c>
       <c r="F59">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G59">
         <v>1365</v>
@@ -7024,7 +7024,7 @@
         <v>109</v>
       </c>
       <c r="F60">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G60">
         <v>1365</v>
@@ -7086,7 +7086,7 @@
         <v>111</v>
       </c>
       <c r="F61">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G61">
         <v>1365</v>
@@ -7148,7 +7148,7 @@
         <v>113</v>
       </c>
       <c r="F62">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G62">
         <v>1365</v>
@@ -7210,7 +7210,7 @@
         <v>115</v>
       </c>
       <c r="F63">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G63">
         <v>1365</v>
@@ -7272,7 +7272,7 @@
         <v>115</v>
       </c>
       <c r="F64">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G64">
         <v>1365</v>
@@ -7334,7 +7334,7 @@
         <v>118</v>
       </c>
       <c r="F65">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G65">
         <v>1365</v>
@@ -7396,7 +7396,7 @@
         <v>118</v>
       </c>
       <c r="F66">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G66">
         <v>1365</v>
@@ -7458,7 +7458,7 @@
         <v>118</v>
       </c>
       <c r="F67">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G67">
         <v>1365</v>
@@ -7520,7 +7520,7 @@
         <v>118</v>
       </c>
       <c r="F68">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G68">
         <v>1365</v>
@@ -7582,7 +7582,7 @@
         <v>123</v>
       </c>
       <c r="F69">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G69">
         <v>1365</v>
@@ -7644,7 +7644,7 @@
         <v>125</v>
       </c>
       <c r="F70">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G70">
         <v>1365</v>
@@ -7706,7 +7706,7 @@
         <v>127</v>
       </c>
       <c r="F71">
-        <v>0.28021874999999996</v>
+        <v>0.3031875</v>
       </c>
       <c r="G71">
         <v>1365</v>
@@ -7768,7 +7768,7 @@
         <v>129</v>
       </c>
       <c r="F72">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G72">
         <v>1365</v>
@@ -7830,7 +7830,7 @@
         <v>127</v>
       </c>
       <c r="F73">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G73">
         <v>1365</v>
@@ -7892,7 +7892,7 @@
         <v>132</v>
       </c>
       <c r="F74">
-        <v>0.28021874999999996</v>
+        <v>0.3031875</v>
       </c>
       <c r="G74">
         <v>1365</v>
@@ -7954,7 +7954,7 @@
         <v>134</v>
       </c>
       <c r="F75">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G75">
         <v>1365</v>
@@ -8016,7 +8016,7 @@
         <v>134</v>
       </c>
       <c r="F76">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G76">
         <v>1365</v>
@@ -8078,7 +8078,7 @@
         <v>134</v>
       </c>
       <c r="F77">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G77">
         <v>1365</v>
@@ -8140,7 +8140,7 @@
         <v>138</v>
       </c>
       <c r="F78">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G78">
         <v>1365</v>
@@ -8202,7 +8202,7 @@
         <v>138</v>
       </c>
       <c r="F79">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G79">
         <v>1365</v>
@@ -8264,7 +8264,7 @@
         <v>132</v>
       </c>
       <c r="F80">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G80">
         <v>1365</v>
@@ -8326,7 +8326,7 @@
         <v>91</v>
       </c>
       <c r="F81">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G81">
         <v>1365</v>
@@ -8388,7 +8388,7 @@
         <v>91</v>
       </c>
       <c r="F82">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G82">
         <v>1365</v>
@@ -8450,7 +8450,7 @@
         <v>144</v>
       </c>
       <c r="F83">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G83">
         <v>1365</v>
@@ -8512,7 +8512,7 @@
         <v>88</v>
       </c>
       <c r="F84">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G84">
         <v>1365</v>
@@ -8574,7 +8574,7 @@
         <v>75</v>
       </c>
       <c r="F85">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G85">
         <v>1365</v>
@@ -8636,7 +8636,7 @@
         <v>75</v>
       </c>
       <c r="F86">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G86">
         <v>1365</v>
@@ -8698,7 +8698,7 @@
         <v>75</v>
       </c>
       <c r="F87">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G87">
         <v>1365</v>
@@ -8760,7 +8760,7 @@
         <v>75</v>
       </c>
       <c r="F88">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G88">
         <v>1365</v>
@@ -8822,7 +8822,7 @@
         <v>81</v>
       </c>
       <c r="F89">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999991</v>
       </c>
       <c r="G89">
         <v>1365</v>
@@ -8884,7 +8884,7 @@
         <v>91</v>
       </c>
       <c r="F90">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G90">
         <v>1365</v>
@@ -8946,7 +8946,7 @@
         <v>91</v>
       </c>
       <c r="F91">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G91">
         <v>1365</v>
@@ -9008,7 +9008,7 @@
         <v>91</v>
       </c>
       <c r="F92">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G92">
         <v>1365</v>
@@ -9070,7 +9070,7 @@
         <v>58</v>
       </c>
       <c r="F93">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G93">
         <v>1365</v>
@@ -9132,7 +9132,7 @@
         <v>58</v>
       </c>
       <c r="F94">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G94">
         <v>1365</v>
@@ -9194,7 +9194,7 @@
         <v>157</v>
       </c>
       <c r="F95">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G95">
         <v>1365</v>
@@ -9256,7 +9256,7 @@
         <v>88</v>
       </c>
       <c r="F96">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G96">
         <v>1365</v>
@@ -9318,7 +9318,7 @@
         <v>75</v>
       </c>
       <c r="F97">
-        <v>0.29089375000000001</v>
+        <v>0.3147375</v>
       </c>
       <c r="G97">
         <v>1365</v>
@@ -9380,7 +9380,7 @@
         <v>99</v>
       </c>
       <c r="F98">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G98">
         <v>1365</v>
@@ -9442,7 +9442,7 @@
         <v>28</v>
       </c>
       <c r="F99">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G99">
         <v>1365</v>
@@ -9504,7 +9504,7 @@
         <v>28</v>
       </c>
       <c r="F100">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G100">
         <v>1365</v>
@@ -9566,7 +9566,7 @@
         <v>88</v>
       </c>
       <c r="F101">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G101">
         <v>1365</v>
@@ -9628,7 +9628,7 @@
         <v>88</v>
       </c>
       <c r="F102">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G102">
         <v>1365</v>
@@ -9690,7 +9690,7 @@
         <v>88</v>
       </c>
       <c r="F103">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G103">
         <v>1365</v>
@@ -9752,7 +9752,7 @@
         <v>85</v>
       </c>
       <c r="F104">
-        <v>0.32025000000000003</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G104">
         <v>1365</v>
@@ -9814,7 +9814,7 @@
         <v>127</v>
       </c>
       <c r="F105">
-        <v>0.32024999999999998</v>
+        <v>0.34649999999999997</v>
       </c>
       <c r="G105">
         <v>1365</v>
@@ -9876,7 +9876,7 @@
         <v>63</v>
       </c>
       <c r="F106">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999991</v>
       </c>
       <c r="G106">
         <v>1365</v>
@@ -9938,7 +9938,7 @@
         <v>60</v>
       </c>
       <c r="F107">
-        <v>0.26687499999999997</v>
+        <v>0.28874999999999995</v>
       </c>
       <c r="G107">
         <v>1365</v>
@@ -10000,7 +10000,7 @@
         <v>81</v>
       </c>
       <c r="F108">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G108">
         <v>1365</v>
@@ -10062,7 +10062,7 @@
         <v>172</v>
       </c>
       <c r="F109">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G109">
         <v>1365</v>
@@ -10124,7 +10124,7 @@
         <v>174</v>
       </c>
       <c r="F110">
-        <v>0.2989</v>
+        <v>0.32340000000000013</v>
       </c>
       <c r="G110">
         <v>1365</v>
@@ -10186,7 +10186,7 @@
         <v>176</v>
       </c>
       <c r="F111">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G111">
         <v>1365</v>
@@ -10248,7 +10248,7 @@
         <v>178</v>
       </c>
       <c r="F112">
-        <v>0.26687499999999997</v>
+        <v>0.28875000000000001</v>
       </c>
       <c r="G112">
         <v>1365</v>
@@ -10310,7 +10310,7 @@
         <v>99</v>
       </c>
       <c r="F113">
-        <v>0.2989</v>
+        <v>0.32340000000000013</v>
       </c>
       <c r="G113">
         <v>1365</v>
@@ -10372,7 +10372,7 @@
         <v>88</v>
       </c>
       <c r="F114">
-        <v>0.30957499999999993</v>
+        <v>0.33494999999999997</v>
       </c>
       <c r="G114">
         <v>1365</v>
@@ -10434,7 +10434,7 @@
         <v>157</v>
       </c>
       <c r="F115">
-        <v>0.20282499999999998</v>
+        <v>0.21945000000000001</v>
       </c>
       <c r="G115">
         <v>1365</v>
@@ -10496,7 +10496,7 @@
         <v>183</v>
       </c>
       <c r="F116">
-        <v>0.29890000000000005</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G116">
         <v>1365</v>
@@ -10558,7 +10558,7 @@
         <v>75</v>
       </c>
       <c r="F117">
-        <v>0.26687499999999997</v>
+        <v>0.28875000000000001</v>
       </c>
       <c r="G117">
         <v>1365</v>
@@ -10620,7 +10620,7 @@
         <v>111</v>
       </c>
       <c r="F118">
-        <v>0.2989</v>
+        <v>0.32340000000000002</v>
       </c>
       <c r="G118">
         <v>1365</v>
@@ -10682,7 +10682,7 @@
         <v>187</v>
       </c>
       <c r="F119">
-        <v>0.27754999999999996</v>
+        <v>0.30030000000000001</v>
       </c>
       <c r="G119">
         <v>1365</v>
@@ -10744,7 +10744,7 @@
         <v>115</v>
       </c>
       <c r="F120">
-        <v>0.26687499999999997</v>
+        <v>0.28875000000000001</v>
       </c>
       <c r="G120">
         <v>1365</v>
@@ -10806,7 +10806,7 @@
         <v>190</v>
       </c>
       <c r="F121">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G121">
         <v>1365</v>
@@ -10868,7 +10868,7 @@
         <v>190</v>
       </c>
       <c r="F122">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G122">
         <v>1365</v>
@@ -10930,7 +10930,7 @@
         <v>193</v>
       </c>
       <c r="F123">
-        <v>0.13610624999999998</v>
+        <v>0.14726249999999999</v>
       </c>
       <c r="G123">
         <v>1365</v>
@@ -10992,7 +10992,7 @@
         <v>174</v>
       </c>
       <c r="F124">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G124">
         <v>1365</v>
@@ -11054,7 +11054,7 @@
         <v>88</v>
       </c>
       <c r="F125">
-        <v>0.14144375000000001</v>
+        <v>0.15303750000000002</v>
       </c>
       <c r="G125">
         <v>1365</v>
@@ -11116,7 +11116,7 @@
         <v>183</v>
       </c>
       <c r="F126">
-        <v>0.15478749999999997</v>
+        <v>0.16747499999999998</v>
       </c>
       <c r="G126">
         <v>1365</v>
@@ -11178,7 +11178,7 @@
         <v>127</v>
       </c>
       <c r="F127">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G127">
         <v>1365</v>
@@ -11240,7 +11240,7 @@
         <v>199</v>
       </c>
       <c r="F128">
-        <v>0.17080000000000001</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G128">
         <v>1365</v>
@@ -11302,7 +11302,7 @@
         <v>201</v>
       </c>
       <c r="F129">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G129">
         <v>1365</v>
@@ -11364,7 +11364,7 @@
         <v>157</v>
       </c>
       <c r="F130">
-        <v>0.19214999999999999</v>
+        <v>0.2079</v>
       </c>
       <c r="G130">
         <v>1365</v>
@@ -11426,7 +11426,7 @@
         <v>88</v>
       </c>
       <c r="F131">
-        <v>0.19214999999999999</v>
+        <v>0.20790000000000003</v>
       </c>
       <c r="G131">
         <v>1365</v>
@@ -11488,7 +11488,7 @@
         <v>91</v>
       </c>
       <c r="F132">
-        <v>0.18948125000000002</v>
+        <v>0.20501250000000001</v>
       </c>
       <c r="G132">
         <v>1365</v>
@@ -11550,7 +11550,7 @@
         <v>206</v>
       </c>
       <c r="F133">
-        <v>0.19214999999999999</v>
+        <v>0.20790000000000003</v>
       </c>
       <c r="G133">
         <v>1365</v>
@@ -11612,7 +11612,7 @@
         <v>88</v>
       </c>
       <c r="F134">
-        <v>0.19214999999999999</v>
+        <v>0.2079</v>
       </c>
       <c r="G134">
         <v>1365</v>
@@ -11674,7 +11674,7 @@
         <v>187</v>
       </c>
       <c r="F135">
-        <v>0.17080000000000001</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G135">
         <v>1365</v>
@@ -11736,7 +11736,7 @@
         <v>113</v>
       </c>
       <c r="F136">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G136">
         <v>1365</v>
@@ -11798,7 +11798,7 @@
         <v>85</v>
       </c>
       <c r="F137">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G137">
         <v>1365</v>
@@ -11860,7 +11860,7 @@
         <v>85</v>
       </c>
       <c r="F138">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G138">
         <v>1365</v>
@@ -11922,7 +11922,7 @@
         <v>213</v>
       </c>
       <c r="F139">
-        <v>0.17080000000000001</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G139">
         <v>1365</v>
@@ -11984,7 +11984,7 @@
         <v>113</v>
       </c>
       <c r="F140">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G140">
         <v>1365</v>
@@ -12046,7 +12046,7 @@
         <v>85</v>
       </c>
       <c r="F141">
-        <v>0.17080000000000001</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G141">
         <v>1365</v>
@@ -12108,7 +12108,7 @@
         <v>85</v>
       </c>
       <c r="F142">
-        <v>0.17080000000000001</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G142">
         <v>1365</v>
@@ -12170,7 +12170,7 @@
         <v>176</v>
       </c>
       <c r="F143">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G143">
         <v>1365</v>
@@ -12232,7 +12232,7 @@
         <v>176</v>
       </c>
       <c r="F144">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G144">
         <v>1365</v>
@@ -12294,7 +12294,7 @@
         <v>220</v>
       </c>
       <c r="F145">
-        <v>0.18147499999999997</v>
+        <v>0.19635000000000005</v>
       </c>
       <c r="G145">
         <v>1365</v>
@@ -12356,7 +12356,7 @@
         <v>138</v>
       </c>
       <c r="F146">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G146">
         <v>1365</v>
@@ -12418,7 +12418,7 @@
         <v>60</v>
       </c>
       <c r="F147">
-        <v>0.17080000000000001</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G147">
         <v>1365</v>
@@ -12480,7 +12480,7 @@
         <v>28</v>
       </c>
       <c r="F148">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G148">
         <v>1365</v>
@@ -12542,7 +12542,7 @@
         <v>206</v>
       </c>
       <c r="F149">
-        <v>0.17080000000000001</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G149">
         <v>1365</v>
@@ -12604,7 +12604,7 @@
         <v>226</v>
       </c>
       <c r="F150">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G150">
         <v>1365</v>
@@ -12666,7 +12666,7 @@
         <v>199</v>
       </c>
       <c r="F151">
-        <v>0.1761375</v>
+        <v>0.19057500000000005</v>
       </c>
       <c r="G151">
         <v>1365</v>
@@ -12728,7 +12728,7 @@
         <v>34</v>
       </c>
       <c r="F152">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G152">
         <v>1365</v>
@@ -12790,7 +12790,7 @@
         <v>230</v>
       </c>
       <c r="F153">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G153">
         <v>1365</v>
@@ -12852,7 +12852,7 @@
         <v>77</v>
       </c>
       <c r="F154">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G154">
         <v>1365</v>
@@ -12914,7 +12914,7 @@
         <v>233</v>
       </c>
       <c r="F155">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G155">
         <v>1365</v>
@@ -13224,7 +13224,7 @@
         <v>31</v>
       </c>
       <c r="F160">
-        <v>0.26687499999999997</v>
+        <v>0.28875000000000001</v>
       </c>
       <c r="G160">
         <v>1365</v>
@@ -13286,7 +13286,7 @@
         <v>132</v>
       </c>
       <c r="F161">
-        <v>0.12809999999999999</v>
+        <v>0.1386</v>
       </c>
       <c r="G161">
         <v>1365</v>
@@ -13348,7 +13348,7 @@
         <v>28</v>
       </c>
       <c r="F162">
-        <v>0.17080000000000001</v>
+        <v>0.18480000000000005</v>
       </c>
       <c r="G162">
         <v>1365</v>
@@ -13410,7 +13410,7 @@
         <v>106</v>
       </c>
       <c r="F163">
-        <v>0.1761375</v>
+        <v>0.19057500000000002</v>
       </c>
       <c r="G163">
         <v>1365</v>
@@ -13472,7 +13472,7 @@
         <v>106</v>
       </c>
       <c r="F164">
-        <v>0.1761375</v>
+        <v>0.19057500000000002</v>
       </c>
       <c r="G164">
         <v>1365</v>
@@ -13534,7 +13534,7 @@
         <v>123</v>
       </c>
       <c r="F165">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G165">
         <v>1365</v>
@@ -13596,7 +13596,7 @@
         <v>123</v>
       </c>
       <c r="F166">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G166">
         <v>1365</v>
@@ -13658,7 +13658,7 @@
         <v>123</v>
       </c>
       <c r="F167">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G167">
         <v>1365</v>
@@ -13720,7 +13720,7 @@
         <v>123</v>
       </c>
       <c r="F168">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G168">
         <v>1365</v>
@@ -13782,7 +13782,7 @@
         <v>123</v>
       </c>
       <c r="F169">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G169">
         <v>1365</v>
@@ -13844,7 +13844,7 @@
         <v>123</v>
       </c>
       <c r="F170">
-        <v>0.181475</v>
+        <v>0.19635000000000002</v>
       </c>
       <c r="G170">
         <v>1365</v>
@@ -13906,7 +13906,7 @@
         <v>96</v>
       </c>
       <c r="F171">
-        <v>0.16012499999999999</v>
+        <v>0.17324999999999999</v>
       </c>
       <c r="G171">
         <v>1365</v>
@@ -13968,7 +13968,7 @@
         <v>88</v>
       </c>
       <c r="F172">
-        <v>0.16546250000000001</v>
+        <v>0.17902500000000005</v>
       </c>
       <c r="G172">
         <v>1365</v>
@@ -14030,7 +14030,7 @@
         <v>157</v>
       </c>
       <c r="F173">
-        <v>0.17080000000000001</v>
+        <v>0.18479999999999999</v>
       </c>
       <c r="G173">
         <v>1365</v>
@@ -14092,7 +14092,7 @@
         <v>213</v>
       </c>
       <c r="F174">
-        <v>0.16012499999999999</v>
+        <v>0.17324999999999999</v>
       </c>
       <c r="G174">
         <v>1365</v>
@@ -14154,7 +14154,7 @@
         <v>199</v>
       </c>
       <c r="F175">
-        <v>0.16012499999999999</v>
+        <v>0.17324999999999999</v>
       </c>
       <c r="G175">
         <v>1365</v>
@@ -14216,7 +14216,7 @@
         <v>132</v>
       </c>
       <c r="F176">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999996</v>
       </c>
       <c r="G176">
         <v>1365</v>
@@ -14278,7 +14278,7 @@
         <v>77</v>
       </c>
       <c r="F177">
-        <v>0.16546250000000001</v>
+        <v>0.17902499999999999</v>
       </c>
       <c r="G177">
         <v>1365</v>
@@ -14332,7 +14332,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1418F312-DC41-46E8-BA43-0688972AE049}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B7D7ED-E64E-4E78-9CA9-633CB853C0A0}">
   <dimension ref="B9:V81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18787,7 +18787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65B57EF4-F622-4D5C-AE6C-987F253AD351}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D3AA4D3-50C6-4EBB-BD49-5893AFEF6A0C}">
   <dimension ref="B9:V441"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18881,7 +18881,7 @@
         <v>0.05</v>
       </c>
       <c r="H11">
-        <v>0.183</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I11">
         <v>4725</v>
@@ -18940,7 +18940,7 @@
         <v>0.1122093157894737</v>
       </c>
       <c r="H12">
-        <v>0.20130000000000001</v>
+        <v>0.21779999999999999</v>
       </c>
       <c r="I12">
         <v>4025</v>
@@ -18999,7 +18999,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="H13">
-        <v>0.18300000000000002</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I13">
         <v>4725</v>
@@ -19058,7 +19058,7 @@
         <v>7.4300763157894759E-2</v>
       </c>
       <c r="H14">
-        <v>0.20130000000000001</v>
+        <v>0.21779999999999999</v>
       </c>
       <c r="I14">
         <v>4025</v>
@@ -19117,7 +19117,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="H15">
-        <v>0.183</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I15">
         <v>4725</v>
@@ -19176,7 +19176,7 @@
         <v>6.823539473684212E-2</v>
       </c>
       <c r="H16">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I16">
         <v>4024.9999999999991</v>
@@ -19235,7 +19235,7 @@
         <v>0.04</v>
       </c>
       <c r="H17">
-        <v>0.183</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I17">
         <v>4725</v>
@@ -19294,7 +19294,7 @@
         <v>0.13647078947368424</v>
       </c>
       <c r="H18">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I18">
         <v>4024.9999999999991</v>
@@ -19353,7 +19353,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="H19">
-        <v>0.183</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I19">
         <v>4725</v>
@@ -19412,7 +19412,7 @@
         <v>5.0039289473684231E-2</v>
       </c>
       <c r="H20">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I20">
         <v>4024.9999999999995</v>
@@ -19471,7 +19471,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
       <c r="H21">
-        <v>0.18300000000000002</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I21">
         <v>4725</v>
@@ -19530,7 +19530,7 @@
         <v>7.4300763157894759E-2</v>
       </c>
       <c r="H22">
-        <v>0.20130000000000001</v>
+        <v>0.21779999999999999</v>
       </c>
       <c r="I22">
         <v>4025</v>
@@ -19589,7 +19589,7 @@
         <v>0.04</v>
       </c>
       <c r="H23">
-        <v>0.183</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I23">
         <v>4725</v>
@@ -19648,7 +19648,7 @@
         <v>6.0653684210526325E-2</v>
       </c>
       <c r="H24">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I24">
         <v>4024.9999999999995</v>
@@ -19707,7 +19707,7 @@
         <v>1.9999999999997797E-3</v>
       </c>
       <c r="H25">
-        <v>0.20205030000000002</v>
+        <v>0.21861180000000002</v>
       </c>
       <c r="L25">
         <v>33</v>
@@ -19757,7 +19757,7 @@
         <v>0.3</v>
       </c>
       <c r="H26">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I26">
         <v>2300</v>
@@ -19816,7 +19816,7 @@
         <v>0.3</v>
       </c>
       <c r="H27">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I27">
         <v>2300</v>
@@ -19875,7 +19875,7 @@
         <v>0.3</v>
       </c>
       <c r="H28">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I28">
         <v>2300</v>
@@ -19934,7 +19934,7 @@
         <v>0.3</v>
       </c>
       <c r="H29">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I29">
         <v>2300</v>
@@ -19993,7 +19993,7 @@
         <v>0.35</v>
       </c>
       <c r="H30">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I30">
         <v>2000</v>
@@ -20052,7 +20052,7 @@
         <v>0.35</v>
       </c>
       <c r="H31">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I31">
         <v>2000</v>
@@ -20111,7 +20111,7 @@
         <v>0.35</v>
       </c>
       <c r="H32">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I32">
         <v>2000</v>
@@ -20170,7 +20170,7 @@
         <v>0.35</v>
       </c>
       <c r="H33">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I33">
         <v>2000</v>
@@ -20229,7 +20229,7 @@
         <v>0.35</v>
       </c>
       <c r="H34">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I34">
         <v>2000</v>
@@ -20288,7 +20288,7 @@
         <v>0.35</v>
       </c>
       <c r="H35">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I35">
         <v>2000</v>
@@ -20347,7 +20347,7 @@
         <v>0.35</v>
       </c>
       <c r="H36">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I36">
         <v>2000</v>
@@ -20406,7 +20406,7 @@
         <v>0.35</v>
       </c>
       <c r="H37">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I37">
         <v>2000</v>
@@ -20465,7 +20465,7 @@
         <v>0.35</v>
       </c>
       <c r="H38">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I38">
         <v>2000</v>
@@ -20524,7 +20524,7 @@
         <v>0.35</v>
       </c>
       <c r="H39">
-        <v>0.21959999999999999</v>
+        <v>0.23759999999999998</v>
       </c>
       <c r="I39">
         <v>2000</v>
@@ -20583,7 +20583,7 @@
         <v>0.67800000000000005</v>
       </c>
       <c r="H40">
-        <v>0.24095</v>
+        <v>0.26070000000000004</v>
       </c>
       <c r="I40">
         <v>2200</v>
@@ -20642,7 +20642,7 @@
         <v>0.51400000000000001</v>
       </c>
       <c r="H41">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I41">
         <v>1000</v>
@@ -20701,7 +20701,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="H42">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I42">
         <v>1000</v>
@@ -20760,7 +20760,7 @@
         <v>0.45300000000000001</v>
       </c>
       <c r="H43">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I43">
         <v>1000</v>
@@ -20819,7 +20819,7 @@
         <v>0.45850000000000002</v>
       </c>
       <c r="H44">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999992</v>
       </c>
       <c r="I44">
         <v>1000</v>
@@ -20878,7 +20878,7 @@
         <v>0.874</v>
       </c>
       <c r="H45">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I45">
         <v>1000</v>
@@ -20937,7 +20937,7 @@
         <v>0.86599999999999999</v>
       </c>
       <c r="H46">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I46">
         <v>1000</v>
@@ -20996,7 +20996,7 @@
         <v>0.878</v>
       </c>
       <c r="H47">
-        <v>0.3538</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I47">
         <v>1000</v>
@@ -21055,7 +21055,7 @@
         <v>0.85</v>
       </c>
       <c r="H48">
-        <v>0.36599999999999994</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I48">
         <v>1000</v>
@@ -21114,7 +21114,7 @@
         <v>0.76600000000000001</v>
       </c>
       <c r="H49">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I49">
         <v>1000</v>
@@ -21173,7 +21173,7 @@
         <v>0.39300000000000002</v>
       </c>
       <c r="H50">
-        <v>0.3538</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I50">
         <v>1000</v>
@@ -21232,7 +21232,7 @@
         <v>0.35</v>
       </c>
       <c r="H51">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I51">
         <v>1000</v>
@@ -21291,7 +21291,7 @@
         <v>0.433</v>
       </c>
       <c r="H52">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I52">
         <v>1000</v>
@@ -21350,7 +21350,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="H53">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I53">
         <v>1000</v>
@@ -21409,7 +21409,7 @@
         <v>0.36399999999999999</v>
       </c>
       <c r="H54">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I54">
         <v>1000</v>
@@ -21468,7 +21468,7 @@
         <v>0.2581</v>
       </c>
       <c r="H55">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I55">
         <v>1150</v>
@@ -21527,7 +21527,7 @@
         <v>0.2581</v>
       </c>
       <c r="H56">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I56">
         <v>1150</v>
@@ -21586,7 +21586,7 @@
         <v>0.72699999999999998</v>
       </c>
       <c r="H57">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I57">
         <v>1000</v>
@@ -21645,7 +21645,7 @@
         <v>0.72699999999999998</v>
       </c>
       <c r="H58">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I58">
         <v>1000</v>
@@ -21704,7 +21704,7 @@
         <v>1.0680000000000001</v>
       </c>
       <c r="H59">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I59">
         <v>1000</v>
@@ -21763,7 +21763,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="H60">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I60">
         <v>1000</v>
@@ -21822,7 +21822,7 @@
         <v>0.45900000000000002</v>
       </c>
       <c r="H61">
-        <v>0.32024999999999998</v>
+        <v>0.34650000000000003</v>
       </c>
       <c r="I61">
         <v>1000</v>
@@ -21881,7 +21881,7 @@
         <v>0.378</v>
       </c>
       <c r="H62">
-        <v>0.27450000000000002</v>
+        <v>0.29700000000000004</v>
       </c>
       <c r="I62">
         <v>1000</v>
@@ -21940,7 +21940,7 @@
         <v>0.76879999999999993</v>
       </c>
       <c r="H63">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I63">
         <v>1000.0000000000001</v>
@@ -21999,7 +21999,7 @@
         <v>0.25</v>
       </c>
       <c r="H64">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I64">
         <v>1150</v>
@@ -22058,7 +22058,7 @@
         <v>0.79100000000000004</v>
       </c>
       <c r="H65">
-        <v>0.35379999999999989</v>
+        <v>0.38279999999999992</v>
       </c>
       <c r="I65">
         <v>1000</v>
@@ -22117,7 +22117,7 @@
         <v>0.77</v>
       </c>
       <c r="H66">
-        <v>0.3538</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I66">
         <v>1000</v>
@@ -22176,7 +22176,7 @@
         <v>0.38600000000000001</v>
       </c>
       <c r="H67">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I67">
         <v>1000</v>
@@ -22235,7 +22235,7 @@
         <v>0.61899999999999999</v>
       </c>
       <c r="H68">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I68">
         <v>1000</v>
@@ -22294,7 +22294,7 @@
         <v>0.32700000000000001</v>
       </c>
       <c r="H69">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I69">
         <v>1000</v>
@@ -22353,7 +22353,7 @@
         <v>0.72799999999999998</v>
       </c>
       <c r="H70">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I70">
         <v>1000</v>
@@ -22412,7 +22412,7 @@
         <v>0.76970000000000005</v>
       </c>
       <c r="H71">
-        <v>0.36599999999999994</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I71">
         <v>999.99999999999989</v>
@@ -22471,7 +22471,7 @@
         <v>0.45539999999999997</v>
       </c>
       <c r="H72">
-        <v>0.36600000000000005</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I72">
         <v>1000</v>
@@ -22530,7 +22530,7 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="H73">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I73">
         <v>1150</v>
@@ -22589,7 +22589,7 @@
         <v>0.38200000000000001</v>
       </c>
       <c r="H74">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I74">
         <v>1000</v>
@@ -22648,7 +22648,7 @@
         <v>0.2475</v>
       </c>
       <c r="H75">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I75">
         <v>1150</v>
@@ -22707,7 +22707,7 @@
         <v>0.93240000000000001</v>
       </c>
       <c r="H76">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I76">
         <v>1000</v>
@@ -22766,7 +22766,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="H77">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I77">
         <v>1000</v>
@@ -22825,7 +22825,7 @@
         <v>1.1319000000000001</v>
       </c>
       <c r="H78">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I78">
         <v>999.99999999999989</v>
@@ -22884,7 +22884,7 @@
         <v>0.495</v>
       </c>
       <c r="H79">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I79">
         <v>1000</v>
@@ -22943,7 +22943,7 @@
         <v>0.59</v>
       </c>
       <c r="H80">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I80">
         <v>1000</v>
@@ -23002,7 +23002,7 @@
         <v>0.59</v>
       </c>
       <c r="H81">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I81">
         <v>1000</v>
@@ -23061,7 +23061,7 @@
         <v>0.495</v>
       </c>
       <c r="H82">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I82">
         <v>1000</v>
@@ -23120,7 +23120,7 @@
         <v>1.1513</v>
       </c>
       <c r="H83">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I83">
         <v>1000</v>
@@ -23179,7 +23179,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="H84">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I84">
         <v>1150</v>
@@ -23238,7 +23238,7 @@
         <v>0.36260000000000003</v>
       </c>
       <c r="H85">
-        <v>0.32024999999999998</v>
+        <v>0.34650000000000003</v>
       </c>
       <c r="I85">
         <v>999.99999999999989</v>
@@ -23297,7 +23297,7 @@
         <v>0.9</v>
       </c>
       <c r="H86">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I86">
         <v>1000</v>
@@ -23356,7 +23356,7 @@
         <v>0.26600000000000001</v>
       </c>
       <c r="H87">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I87">
         <v>1150</v>
@@ -23415,7 +23415,7 @@
         <v>0.505</v>
       </c>
       <c r="H88">
-        <v>0.32024999999999998</v>
+        <v>0.34650000000000003</v>
       </c>
       <c r="I88">
         <v>1000</v>
@@ -23474,7 +23474,7 @@
         <v>0.5</v>
       </c>
       <c r="H89">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I89">
         <v>1000</v>
@@ -23533,7 +23533,7 @@
         <v>0.495</v>
       </c>
       <c r="H90">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I90">
         <v>1000</v>
@@ -23592,7 +23592,7 @@
         <v>0.495</v>
       </c>
       <c r="H91">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I91">
         <v>1000</v>
@@ -23651,7 +23651,7 @@
         <v>0.61499999999999999</v>
       </c>
       <c r="H92">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I92">
         <v>1000</v>
@@ -23710,7 +23710,7 @@
         <v>0.54900000000000004</v>
       </c>
       <c r="H93">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I93">
         <v>1000</v>
@@ -23769,7 +23769,7 @@
         <v>0.56459999999999999</v>
       </c>
       <c r="H94">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I94">
         <v>1000</v>
@@ -23828,7 +23828,7 @@
         <v>0.252</v>
       </c>
       <c r="H95">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I95">
         <v>1150</v>
@@ -23887,7 +23887,7 @@
         <v>0.252</v>
       </c>
       <c r="H96">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I96">
         <v>1150</v>
@@ -23946,7 +23946,7 @@
         <v>0.65600000000000003</v>
       </c>
       <c r="H97">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I97">
         <v>1000</v>
@@ -24005,7 +24005,7 @@
         <v>0.32400000000000001</v>
       </c>
       <c r="H98">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I98">
         <v>1000</v>
@@ -24064,7 +24064,7 @@
         <v>0.57699999999999996</v>
       </c>
       <c r="H99">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I99">
         <v>1000</v>
@@ -24123,7 +24123,7 @@
         <v>0.57799999999999996</v>
       </c>
       <c r="H100">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I100">
         <v>1000</v>
@@ -24182,7 +24182,7 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="H101">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I101">
         <v>1000</v>
@@ -24241,7 +24241,7 @@
         <v>0.54800000000000004</v>
       </c>
       <c r="H102">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I102">
         <v>1000</v>
@@ -24300,7 +24300,7 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="H103">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999992</v>
       </c>
       <c r="I103">
         <v>1000</v>
@@ -24359,7 +24359,7 @@
         <v>0.3</v>
       </c>
       <c r="H104">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I104">
         <v>1150</v>
@@ -24418,7 +24418,7 @@
         <v>0.252</v>
       </c>
       <c r="H105">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I105">
         <v>1150</v>
@@ -24477,7 +24477,7 @@
         <v>0.252</v>
       </c>
       <c r="H106">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I106">
         <v>1150</v>
@@ -24536,7 +24536,7 @@
         <v>0.58950000000000002</v>
       </c>
       <c r="H107">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I107">
         <v>1000</v>
@@ -24595,7 +24595,7 @@
         <v>0.58950000000000002</v>
       </c>
       <c r="H108">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I108">
         <v>1000</v>
@@ -24654,7 +24654,7 @@
         <v>0.53700000000000003</v>
       </c>
       <c r="H109">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I109">
         <v>1000</v>
@@ -24713,7 +24713,7 @@
         <v>0.625</v>
       </c>
       <c r="H110">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I110">
         <v>1000</v>
@@ -24772,7 +24772,7 @@
         <v>0.495</v>
       </c>
       <c r="H111">
-        <v>0.33245000000000002</v>
+        <v>0.35970000000000002</v>
       </c>
       <c r="I111">
         <v>1000</v>
@@ -24831,7 +24831,7 @@
         <v>0.27789999999999998</v>
       </c>
       <c r="H112">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I112">
         <v>1150</v>
@@ -24890,7 +24890,7 @@
         <v>0.28299999999999997</v>
       </c>
       <c r="H113">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I113">
         <v>1150</v>
@@ -24949,7 +24949,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="H114">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I114">
         <v>1150</v>
@@ -25008,7 +25008,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="H115">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I115">
         <v>1150</v>
@@ -25067,7 +25067,7 @@
         <v>0.248</v>
       </c>
       <c r="H116">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I116">
         <v>1150</v>
@@ -25126,7 +25126,7 @@
         <v>0.26200000000000001</v>
       </c>
       <c r="H117">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I117">
         <v>1150</v>
@@ -25185,7 +25185,7 @@
         <v>0.37139999999999995</v>
       </c>
       <c r="H118">
-        <v>0.36600000000000005</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I118">
         <v>1000.0000000000001</v>
@@ -25244,7 +25244,7 @@
         <v>0.34100000000000003</v>
       </c>
       <c r="H119">
-        <v>0.36599999999999999</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="I119">
         <v>1000</v>
@@ -25303,7 +25303,7 @@
         <v>0.45850000000000002</v>
       </c>
       <c r="H120">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999992</v>
       </c>
       <c r="I120">
         <v>1000</v>
@@ -25362,7 +25362,7 @@
         <v>0.52200000000000002</v>
       </c>
       <c r="H121">
-        <v>0.30499999999999999</v>
+        <v>0.32999999999999996</v>
       </c>
       <c r="I121">
         <v>1150</v>
@@ -25421,7 +25421,7 @@
         <v>0.22700000000000001</v>
       </c>
       <c r="H122">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I122">
         <v>1150</v>
@@ -25480,7 +25480,7 @@
         <v>0.23200000000000001</v>
       </c>
       <c r="H123">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I123">
         <v>1150</v>
@@ -25539,7 +25539,7 @@
         <v>0.33550000000000002</v>
       </c>
       <c r="H124">
-        <v>0.30499999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="I124">
         <v>1150</v>
@@ -25598,7 +25598,7 @@
         <v>0.17560000000000001</v>
       </c>
       <c r="H125">
-        <v>0.34160000000000001</v>
+        <v>0.3696000000000001</v>
       </c>
       <c r="I125">
         <v>1150</v>
@@ -25657,7 +25657,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H126">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I126">
         <v>1150</v>
@@ -25716,7 +25716,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="H127">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I127">
         <v>1150</v>
@@ -25775,7 +25775,7 @@
         <v>0.45200000000000001</v>
       </c>
       <c r="H128">
-        <v>0.30499999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="I128">
         <v>1150</v>
@@ -25834,7 +25834,7 @@
         <v>0.20499999999999999</v>
       </c>
       <c r="H129">
-        <v>0.34160000000000001</v>
+        <v>0.3696000000000001</v>
       </c>
       <c r="I129">
         <v>1150</v>
@@ -25893,7 +25893,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="H130">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I130">
         <v>1150</v>
@@ -25952,7 +25952,7 @@
         <v>0.15</v>
       </c>
       <c r="H131">
-        <v>0.35379999999999995</v>
+        <v>0.38279999999999997</v>
       </c>
       <c r="I131">
         <v>1150</v>
@@ -26011,7 +26011,7 @@
         <v>0.23980000000000001</v>
       </c>
       <c r="H132">
-        <v>0.23180000000000001</v>
+        <v>0.25080000000000002</v>
       </c>
       <c r="I132">
         <v>1150</v>
@@ -26070,7 +26070,7 @@
         <v>0.11799999999999999</v>
       </c>
       <c r="H133">
-        <v>0.34160000000000007</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I133">
         <v>1150</v>
@@ -26129,7 +26129,7 @@
         <v>0.14399999999999999</v>
       </c>
       <c r="H134">
-        <v>0.30499999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="I134">
         <v>1150</v>
@@ -26188,7 +26188,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
       <c r="H135">
-        <v>0.34160000000000001</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="I135">
         <v>1150</v>
@@ -26247,7 +26247,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="H136">
-        <v>0.31719999999999998</v>
+        <v>0.34320000000000001</v>
       </c>
       <c r="I136">
         <v>1150</v>
@@ -26306,7 +26306,7 @@
         <v>0.22</v>
       </c>
       <c r="H137">
-        <v>0.30499999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="I137">
         <v>1150</v>
@@ -26365,7 +26365,7 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="H138">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I138">
         <v>919.99999999999989</v>
@@ -26424,7 +26424,7 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="H139">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I139">
         <v>919.99999999999989</v>
@@ -26483,7 +26483,7 @@
         <v>0.05</v>
       </c>
       <c r="H140">
-        <v>0.15554999999999999</v>
+        <v>0.16830000000000001</v>
       </c>
       <c r="I140">
         <v>1080</v>
@@ -26542,7 +26542,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="H141">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I141">
         <v>919.99999999999989</v>
@@ -26601,7 +26601,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="H142">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I142">
         <v>919.99999999999989</v>
@@ -26660,7 +26660,7 @@
         <v>0.17100000000000001</v>
       </c>
       <c r="H143">
-        <v>0.16165000000000002</v>
+        <v>0.17490000000000003</v>
       </c>
       <c r="I143">
         <v>919.99999999999989</v>
@@ -26719,7 +26719,7 @@
         <v>5.96E-2</v>
       </c>
       <c r="H144">
-        <v>0.17689999999999997</v>
+        <v>0.19139999999999999</v>
       </c>
       <c r="I144">
         <v>919.99999999999989</v>
@@ -26778,7 +26778,7 @@
         <v>0.3</v>
       </c>
       <c r="H145">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I145">
         <v>919.99999999999977</v>
@@ -26837,7 +26837,7 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="H146">
-        <v>0.19520000000000001</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I146">
         <v>919.99999999999989</v>
@@ -26896,7 +26896,7 @@
         <v>0.2</v>
       </c>
       <c r="H147">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I147">
         <v>919.99999999999989</v>
@@ -26955,7 +26955,7 @@
         <v>0.3634</v>
       </c>
       <c r="H148">
-        <v>0.21960000000000002</v>
+        <v>0.23760000000000001</v>
       </c>
       <c r="I148">
         <v>1100</v>
@@ -27014,7 +27014,7 @@
         <v>0.44160000000000005</v>
       </c>
       <c r="H149">
-        <v>0.21959999999999999</v>
+        <v>0.23760000000000003</v>
       </c>
       <c r="I149">
         <v>1100</v>
@@ -27073,7 +27073,7 @@
         <v>0.13090000000000002</v>
       </c>
       <c r="H150">
-        <v>0.21654999999999999</v>
+        <v>0.23430000000000001</v>
       </c>
       <c r="I150">
         <v>1265</v>
@@ -27132,7 +27132,7 @@
         <v>0.14099999999999999</v>
       </c>
       <c r="H151">
-        <v>0.21959999999999999</v>
+        <v>0.23760000000000003</v>
       </c>
       <c r="I151">
         <v>1265</v>
@@ -27191,7 +27191,7 @@
         <v>0.22</v>
       </c>
       <c r="H152">
-        <v>0.21959999999999999</v>
+        <v>0.23760000000000001</v>
       </c>
       <c r="I152">
         <v>1265</v>
@@ -27250,7 +27250,7 @@
         <v>0.3</v>
       </c>
       <c r="H153">
-        <v>0.19520000000000001</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I153">
         <v>1380</v>
@@ -27309,7 +27309,7 @@
         <v>0.3</v>
       </c>
       <c r="H154">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I154">
         <v>1380</v>
@@ -27368,7 +27368,7 @@
         <v>0.35</v>
       </c>
       <c r="H155">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I155">
         <v>1200</v>
@@ -27427,7 +27427,7 @@
         <v>0.35</v>
       </c>
       <c r="H156">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I156">
         <v>1200</v>
@@ -27486,7 +27486,7 @@
         <v>0.3</v>
       </c>
       <c r="H157">
-        <v>0.19520000000000001</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I157">
         <v>1380</v>
@@ -27545,7 +27545,7 @@
         <v>0.25</v>
       </c>
       <c r="H158">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I158">
         <v>1380</v>
@@ -27604,7 +27604,7 @@
         <v>0.3</v>
       </c>
       <c r="H159">
-        <v>0.19520000000000001</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I159">
         <v>1380</v>
@@ -27663,7 +27663,7 @@
         <v>0.3</v>
       </c>
       <c r="H160">
-        <v>0.19520000000000001</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I160">
         <v>1380</v>
@@ -27722,7 +27722,7 @@
         <v>0.25</v>
       </c>
       <c r="H161">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I161">
         <v>1380</v>
@@ -27781,7 +27781,7 @@
         <v>0.25</v>
       </c>
       <c r="H162">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I162">
         <v>1380</v>
@@ -27840,7 +27840,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="H163">
-        <v>0.20739999999999997</v>
+        <v>0.22440000000000004</v>
       </c>
       <c r="I163">
         <v>1380</v>
@@ -27899,7 +27899,7 @@
         <v>0.15</v>
       </c>
       <c r="H164">
-        <v>0.183</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I164">
         <v>1380</v>
@@ -27958,7 +27958,7 @@
         <v>0.15</v>
       </c>
       <c r="H165">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I165">
         <v>1380</v>
@@ -28017,7 +28017,7 @@
         <v>0.316</v>
       </c>
       <c r="H166">
-        <v>0.19520000000000001</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I166">
         <v>1380</v>
@@ -28076,7 +28076,7 @@
         <v>0.13369999999999999</v>
       </c>
       <c r="H167">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I167">
         <v>1380</v>
@@ -28135,7 +28135,7 @@
         <v>0.63200000000000001</v>
       </c>
       <c r="H168">
-        <v>0.19520000000000001</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I168">
         <v>1380</v>
@@ -28194,7 +28194,7 @@
         <v>0.115</v>
       </c>
       <c r="H169">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I169">
         <v>1380</v>
@@ -28253,7 +28253,7 @@
         <v>0.32</v>
       </c>
       <c r="H170">
-        <v>0.20129999999999998</v>
+        <v>0.21780000000000005</v>
       </c>
       <c r="I170">
         <v>1380</v>
@@ -28312,7 +28312,7 @@
         <v>0.129</v>
       </c>
       <c r="H171">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I171">
         <v>1380</v>
@@ -28371,7 +28371,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="H172">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I172">
         <v>1380</v>
@@ -28430,7 +28430,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="H173">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I173">
         <v>1380</v>
@@ -28489,7 +28489,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="H174">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I174">
         <v>1380</v>
@@ -32873,7 +32873,7 @@
         <v>0.27500000000000002</v>
       </c>
       <c r="H251">
-        <v>0.30499999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="I251">
         <v>1265</v>
@@ -32932,7 +32932,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="H252">
-        <v>0.1464</v>
+        <v>0.15840000000000001</v>
       </c>
       <c r="I252">
         <v>1035</v>
@@ -32991,7 +32991,7 @@
         <v>0.32300000000000001</v>
       </c>
       <c r="H253">
-        <v>0.19520000000000001</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="I253">
         <v>1300</v>
@@ -33050,7 +33050,7 @@
         <v>0.35</v>
       </c>
       <c r="H254">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I254">
         <v>1300</v>
@@ -33109,7 +33109,7 @@
         <v>0.35</v>
       </c>
       <c r="H255">
-        <v>0.20130000000000001</v>
+        <v>0.21780000000000002</v>
       </c>
       <c r="I255">
         <v>1300</v>
@@ -33168,7 +33168,7 @@
         <v>0.35</v>
       </c>
       <c r="H256">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I256">
         <v>1300</v>
@@ -33227,7 +33227,7 @@
         <v>0.35</v>
       </c>
       <c r="H257">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I257">
         <v>1300</v>
@@ -33286,7 +33286,7 @@
         <v>0.35</v>
       </c>
       <c r="H258">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I258">
         <v>1300</v>
@@ -33345,7 +33345,7 @@
         <v>0.35</v>
       </c>
       <c r="H259">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I259">
         <v>1300</v>
@@ -33404,7 +33404,7 @@
         <v>0.35</v>
       </c>
       <c r="H260">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I260">
         <v>1300</v>
@@ -33463,7 +33463,7 @@
         <v>0.35</v>
       </c>
       <c r="H261">
-        <v>0.2074</v>
+        <v>0.22440000000000002</v>
       </c>
       <c r="I261">
         <v>1300</v>
@@ -33522,7 +33522,7 @@
         <v>0.48399999999999999</v>
       </c>
       <c r="H262">
-        <v>0.183</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I262">
         <v>1494.9999999999998</v>
@@ -33581,7 +33581,7 @@
         <v>0.32</v>
       </c>
       <c r="H263">
-        <v>0.18909999999999999</v>
+        <v>0.20460000000000003</v>
       </c>
       <c r="I263">
         <v>1494.9999999999998</v>
@@ -33640,7 +33640,7 @@
         <v>0.32</v>
       </c>
       <c r="H264">
-        <v>0.19520000000000001</v>
+        <v>0.2112</v>
       </c>
       <c r="I264">
         <v>1494.9999999999998</v>
@@ -33699,7 +33699,7 @@
         <v>0.316</v>
       </c>
       <c r="H265">
-        <v>0.183</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I265">
         <v>1494.9999999999998</v>
@@ -33758,7 +33758,7 @@
         <v>0.113</v>
       </c>
       <c r="H266">
-        <v>0.183</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="I266">
         <v>1494.9999999999998</v>
@@ -33817,7 +33817,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="H267">
-        <v>0.18909999999999999</v>
+        <v>0.20459999999999998</v>
       </c>
       <c r="I267">
         <v>1494.9999999999998</v>
@@ -33876,7 +33876,7 @@
         <v>0.3</v>
       </c>
       <c r="H268">
-        <v>0.18909999999999999</v>
+        <v>0.2046</v>
       </c>
       <c r="I268">
         <v>1494.9999999999998</v>
@@ -34024,7 +34024,7 @@
         <v>14</v>
       </c>
       <c r="R270" t="s">
-        <v>606</v>
+        <v>504</v>
       </c>
       <c r="S270" t="s">
         <v>498</v>
@@ -34086,7 +34086,7 @@
         <v>14</v>
       </c>
       <c r="R271" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="S271" t="s">
         <v>498</v>
@@ -34272,7 +34272,7 @@
         <v>14</v>
       </c>
       <c r="R274" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="S274" t="s">
         <v>498</v>
@@ -34334,7 +34334,7 @@
         <v>14</v>
       </c>
       <c r="R275" t="s">
-        <v>606</v>
+        <v>504</v>
       </c>
       <c r="S275" t="s">
         <v>498</v>
@@ -38116,7 +38116,7 @@
         <v>14</v>
       </c>
       <c r="R336" t="s">
-        <v>606</v>
+        <v>504</v>
       </c>
       <c r="S336" t="s">
         <v>498</v>
@@ -38178,7 +38178,7 @@
         <v>14</v>
       </c>
       <c r="R337" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="S337" t="s">
         <v>498</v>
@@ -38798,7 +38798,7 @@
         <v>14</v>
       </c>
       <c r="R347" t="s">
-        <v>606</v>
+        <v>504</v>
       </c>
       <c r="S347" t="s">
         <v>498</v>
@@ -38860,7 +38860,7 @@
         <v>14</v>
       </c>
       <c r="R348" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="S348" t="s">
         <v>498</v>
@@ -38922,7 +38922,7 @@
         <v>14</v>
       </c>
       <c r="R349" t="s">
-        <v>606</v>
+        <v>504</v>
       </c>
       <c r="S349" t="s">
         <v>498</v>
@@ -38984,7 +38984,7 @@
         <v>14</v>
       </c>
       <c r="R350" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="S350" t="s">
         <v>498</v>
@@ -42775,7 +42775,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C60CC5-BB93-4D53-BD77-6B7EDF959D70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51B074D1-6178-4D38-831D-829351CF4A61}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
